--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>淞虹路377号 长宁ArtPark大融城</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/XmP03Vf31701070803044.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tprwYGIB1705976768947.jpeg</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1158</v>
+        <v>1172</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>908</v>
+        <v>931</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>637</v>
+        <v>672</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1291</v>
+        <v>1300</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1366,38 +1366,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,30 +1407,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1205</v>
+        <v>90</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1453,30 +1453,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>189</v>
+        <v>1212</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>111</v>
+        <v>231</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1550,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2471</v>
+        <v>116</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,38 +1596,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2486</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
         <v>1</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1637,30 +1637,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>246</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1729,30 +1729,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1780,38 +1780,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1826,38 +1826,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>865</v>
+        <v>43</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>16</v>
+        <v>875</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,30 +1913,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1959,30 +1959,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2005,30 +2005,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -2056,25 +2056,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -2097,41 +2097,87 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>188</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>8</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F38" t="n">
+        <v>11</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2148,7 +2194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2226,7 +2272,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2345,30 +2391,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·七音阿卡莉 NANAOAKARI 2024 专场演出</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.23 20:00-01.23 22:00</t>
+          <t>2024.01.26 19:30-01.26 21:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -2376,12 +2422,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79641</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/CoNbgCpO1703644783043.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
         </is>
       </c>
     </row>
@@ -2391,43 +2437,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·Azurock」Azurose ACG Cover Live</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>愚园路1398号 育音堂音乐公园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:30</t>
+          <t>2024.01.27 19:00-01.27 21:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>161</v>
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
         </is>
       </c>
     </row>
@@ -2442,38 +2488,38 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·Azurock」Azurose ACG Cover Live</t>
+          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>愚园路1398号 育音堂音乐公园</t>
+          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 19:00-01.27 21:30</t>
+          <t>2024.01.27 15:30-01.27 20:55</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
         </is>
       </c>
     </row>
@@ -2488,25 +2534,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
+          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 15:30-01.27 20:55</t>
+          <t>2024.01.27 18:30-01.27 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>298</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -2514,12 +2560,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
         </is>
       </c>
     </row>
@@ -2529,30 +2575,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 18:30-01.27 21:00</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>298</v>
+        <v>631</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -2560,12 +2606,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2575,43 +2621,43 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>620</v>
+        <v>339</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2621,30 +2667,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>329</v>
+        <v>2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -2652,12 +2698,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2667,30 +2713,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -2698,12 +2744,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/dp013A4p1704783993628.png</t>
         </is>
       </c>
     </row>
@@ -2713,30 +2759,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -2744,12 +2790,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/dp013A4p1704783993628.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,43 +2805,43 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2856,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2820,15 +2866,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>235</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -2836,12 +2882,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2916,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2897,43 +2943,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2994,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2958,7 +3004,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2966,7 +3012,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -2974,12 +3020,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3054,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3100,7 +3146,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3173,30 +3219,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>271</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -3204,12 +3250,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,30 +3265,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>140</v>
+        <v>349</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -3250,12 +3296,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3265,43 +3311,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3311,26 +3357,26 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3342,12 +3388,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3357,26 +3403,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3384,16 +3430,16 @@
         </is>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3403,41 +3449,87 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.04.20 19:30-04.20 21:30</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>2024-04-26</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>10</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F29" t="n">
+        <v>11</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
@@ -3624,7 +3716,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3670,7 +3762,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1984</v>
+        <v>1995</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3716,7 +3808,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2082</v>
+        <v>2101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3762,7 +3854,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3804,11 +3896,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-01.31 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3899,30 +3991,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上海·日漫咖啡体验</t>
+          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>虹桥路1438号高岛屋百货6楼 OASIS书吧</t>
+          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2023.01.12 10:00-2024.02.29 22:00</t>
+          <t>2023.10.16 10:00-2024.10.15 21:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1726</v>
+        <v>69</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>996</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -3930,12 +4022,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202106/okF9H2Uj1623911727887.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
       </c>
     </row>
@@ -3945,30 +4037,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -3976,12 +4068,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3991,30 +4083,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>漕宝路3055号 宝龙美术馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.11.02 10:00-2024.01.28 18:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>121</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -4022,12 +4114,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
         </is>
       </c>
     </row>
@@ -4037,30 +4129,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
+          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>漕宝路3055号 宝龙美术馆</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.11.02 10:00-2024.01.28 18:00</t>
+          <t>2023.12.01 00:00-2024.01.31 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>1995</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -4068,12 +4160,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
       </c>
     </row>
@@ -4083,26 +4175,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1984</v>
+        <v>2101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4114,12 +4206,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4129,30 +4221,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2082</v>
+        <v>1673</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -4160,12 +4252,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4175,30 +4267,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1672</v>
+        <v>24</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -4206,12 +4298,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4221,12 +4313,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4236,11 +4328,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4252,12 +4344,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4267,30 +4359,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2023.12.31 00:00-2024.01.29 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>824</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -4298,12 +4390,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
         </is>
       </c>
     </row>
@@ -4313,30 +4405,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2023.12.31 00:00-2024.01.29 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>820</v>
+        <v>726</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -4344,12 +4436,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4359,43 +4451,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-26</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-01.31 23:59</t>
+          <t>2024.01.26 19:30-01.26 21:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>703</v>
+        <v>163</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
         </is>
       </c>
     </row>
@@ -4405,43 +4497,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·25时主题同人茶会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>沪太路3100号 尚大国际</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:30</t>
+          <t>2024.01.27 12:00-01.27 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
         </is>
       </c>
     </row>
@@ -4456,25 +4548,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·25时主题同人茶会</t>
+          <t>上海·Azurock」Azurose ACG Cover Live</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>沪太路3100号 尚大国际</t>
+          <t>愚园路1398号 育音堂音乐公园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.27 18:00</t>
+          <t>2024.01.27 19:00-01.27 21:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>126</v>
+        <v>60</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -4482,12 +4574,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
         </is>
       </c>
     </row>
@@ -4502,25 +4594,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·Azurock」Azurose ACG Cover Live</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>愚园路1398号 育音堂音乐公园</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.01.27 19:00-01.27 21:30</t>
+          <t>2024.01.27 13:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>390</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -4528,12 +4620,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/tprwYGIB1705976768947.jpeg</t>
         </is>
       </c>
     </row>
@@ -4548,25 +4640,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·同好召集令火影only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>淞虹路377号 长宁ArtPark大融城</t>
+          <t>市真南路1199弄1号 智创TOP综合体产城</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.01.27 13:00-01.28 19:00</t>
+          <t>2024.01.27 10:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>369</v>
+        <v>543</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -4574,12 +4666,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/XmP03Vf31701070803044.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
         </is>
       </c>
     </row>
@@ -4594,25 +4686,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·咒术only-幽暗之森1.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.27 10:00-01.27 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>527</v>
+        <v>251</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -4620,12 +4712,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
         </is>
       </c>
     </row>
@@ -4640,38 +4732,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·咒术only-幽暗之森1.0</t>
+          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:00</t>
+          <t>2024.01.27 15:30-01.27 20:55</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>248</v>
+        <v>31</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
         </is>
       </c>
     </row>
@@ -4686,38 +4778,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.01.27 15:30-01.27 20:55</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>1172</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -4732,25 +4824,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·魔都寒假漫展-CF01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.27 10:00-01.28 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1158</v>
+        <v>931</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -4758,12 +4850,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
         </is>
       </c>
     </row>
@@ -4778,38 +4870,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.27 18:30-01.27 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>909</v>
+        <v>298</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>278</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
         </is>
       </c>
     </row>
@@ -4819,43 +4911,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
+          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.01.27 18:30-01.27 21:00</t>
+          <t>2024.01.28 14:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>298</v>
+        <v>428</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
         </is>
       </c>
     </row>
@@ -4865,30 +4957,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>420</v>
+        <v>186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -4896,12 +4988,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -4911,43 +5003,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>183</v>
+        <v>631</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4957,43 +5049,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>620</v>
+        <v>672</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -5008,25 +5100,25 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>637</v>
+        <v>30</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -5034,12 +5126,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -5049,30 +5141,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>339</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -5080,12 +5172,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5206,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5141,30 +5233,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>84</v>
+        <v>1212</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -5172,12 +5264,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -5187,30 +5279,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1205</v>
+        <v>231</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -5218,12 +5310,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -5233,30 +5325,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -5264,12 +5356,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -5284,25 +5376,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -5310,12 +5402,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/dp013A4p1704783993628.png</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5436,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2471</v>
+        <v>2486</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5371,30 +5463,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>199</v>
+        <v>4</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -5402,12 +5494,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5417,30 +5509,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -5448,12 +5540,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -5468,38 +5560,38 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>226</v>
+        <v>252</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5509,43 +5601,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5555,30 +5647,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -5586,12 +5678,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5606,38 +5698,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5652,38 +5744,38 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>865</v>
+        <v>43</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5693,30 +5785,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>875</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -5724,12 +5816,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5744,25 +5836,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -5770,12 +5862,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5785,30 +5877,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -5816,12 +5908,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5942,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -5877,30 +5969,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -5908,12 +6000,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5923,43 +6015,43 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -5969,26 +6061,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>171</v>
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6000,12 +6092,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6126,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6080,7 +6172,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -6126,7 +6218,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -6172,7 +6264,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1673</v>
+        <v>1679</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1172</v>
+        <v>1190</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>672</v>
+        <v>701</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1212</v>
+        <v>6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>231</v>
+        <v>1221</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1545,30 +1545,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>116</v>
+        <v>263</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,38 +1596,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2486</v>
+        <v>117</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1642,38 +1642,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ZDx5KYdG1706086833692.png</t>
         </is>
       </c>
     </row>
@@ -1683,43 +1683,43 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>252</v>
+        <v>2498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1729,30 +1729,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·霓虹次元·二次元夜场3.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.02.24 15:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ksdMGr6X1706067357226.jpeg</t>
         </is>
       </c>
     </row>
@@ -1775,30 +1775,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1821,43 +1821,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>256</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1867,30 +1867,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>875</v>
+        <v>140</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,30 +1913,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1959,43 +1959,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -2005,30 +2005,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>148</v>
+        <v>882</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -2051,30 +2051,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -2097,30 +2097,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2143,41 +2143,179 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2024-04-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>曹杨路1888号 复悦荟</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2024.04.27 10:00-04.27 17:00</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>150</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>军工路1076号 纪希片场(秀场)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.02 17:00</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>196</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="F41" t="n">
+        <v>13</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="H38" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2194,7 +2332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,7 +2456,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2410,7 +2548,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2456,7 +2594,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2502,7 +2640,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2594,7 +2732,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2640,7 +2778,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2690,7 +2828,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已停售</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -2778,7 +2916,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2870,7 +3008,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2897,43 +3035,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3086,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2958,15 +3096,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -2974,12 +3112,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2989,30 +3127,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -3020,12 +3158,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -3035,30 +3173,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -3066,12 +3204,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -3086,25 +3224,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>533</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -3112,12 +3250,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -3132,25 +3270,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>471</v>
+        <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -3158,12 +3296,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -3178,21 +3316,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3204,12 +3342,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,30 +3357,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>397</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>480</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -3250,12 +3388,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3265,30 +3403,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>349</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -3296,12 +3434,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -3311,30 +3449,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -3342,12 +3480,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -3357,43 +3495,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3403,26 +3541,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>172</v>
+        <v>10</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3434,12 +3572,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3449,26 +3587,26 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3476,16 +3614,16 @@
         </is>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3495,41 +3633,87 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.04.20 19:30-04.20 21:30</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>2024-04-26</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>11</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
@@ -3546,7 +3730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3624,7 +3808,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3670,7 +3854,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3762,7 +3946,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3808,7 +3992,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2101</v>
+        <v>2119</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3854,7 +4038,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3900,7 +4084,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3918,6 +4102,236 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-01-21</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上海·JOYPOLIS世嘉都市乐园</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>中山北路3300号 上海月星环球港</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2024.01.21 10:00-02.20 21:00</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-01-22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2024.01.22 14:00-03.03 18:40</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-01-27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2024.01.27 00:00-03.31 23:59</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>633</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2024.02.01 00:00-03.01 23:59</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024.02.02 00:00-03.10 23:59</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -3932,7 +4346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4010,7 +4424,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4102,7 +4516,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4148,7 +4562,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1995</v>
+        <v>2004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4194,7 +4608,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2101</v>
+        <v>2119</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4240,7 +4654,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1673</v>
+        <v>1679</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4332,7 +4746,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4378,7 +4792,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4424,7 +4838,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>726</v>
+        <v>752</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4470,7 +4884,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4516,7 +4930,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4562,7 +4976,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -4608,7 +5022,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -4654,7 +5068,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -4700,7 +5114,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -4746,7 +5160,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -4792,7 +5206,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1172</v>
+        <v>1190</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -4838,7 +5252,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>931</v>
+        <v>957</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4930,7 +5344,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -5022,7 +5436,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -5068,7 +5482,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>672</v>
+        <v>701</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -5114,7 +5528,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -5160,7 +5574,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -5206,7 +5620,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5252,7 +5666,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1212</v>
+        <v>1221</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -5298,7 +5712,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -5344,7 +5758,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -5436,7 +5850,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2486</v>
+        <v>2498</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5482,7 +5896,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -5528,7 +5942,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -5574,7 +5988,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -5601,43 +6015,43 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>235</v>
+        <v>140</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5647,30 +6061,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>133</v>
+        <v>41</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -5678,12 +6092,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5698,38 +6112,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5744,38 +6158,38 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>882</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5785,30 +6199,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>875</v>
+        <v>43</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -5816,12 +6230,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5836,25 +6250,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -5862,12 +6276,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5877,30 +6291,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -5908,12 +6322,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5923,30 +6337,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -5954,12 +6368,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -5969,43 +6383,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -6015,30 +6429,30 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -6046,12 +6460,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -6061,26 +6475,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -6088,16 +6502,16 @@
         </is>
       </c>
       <c r="H47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -6107,30 +6521,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -6138,12 +6552,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -6153,30 +6567,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -6184,102 +6598,10 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>上海·魔都野良神only</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>南京东路830号 第一百货</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>188</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1679</v>
+        <v>1686</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -676,25 +676,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·同好召集令火影only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>市真南路1199弄1号 智创TOP综合体产城</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 13:00-01.28 19:00</t>
+          <t>2024.01.27 10:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>411</v>
+        <v>560</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -702,12 +702,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tprwYGIB1705976768947.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
         </is>
       </c>
     </row>
@@ -722,25 +722,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·咒术only-幽暗之森1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.27 10:00-01.27 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>554</v>
+        <v>257</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -748,12 +748,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
         </is>
       </c>
     </row>
@@ -768,25 +768,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·咒术only-幽暗之森1.0</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:00</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>252</v>
+        <v>1204</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -794,12 +794,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,25 +814,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·魔都寒假漫展-CF01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.27 10:00-01.28 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1190</v>
+        <v>971</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -840,12 +840,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,30 +855,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.28 14:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>957</v>
+        <v>442</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -886,12 +886,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
         </is>
       </c>
     </row>
@@ -906,25 +906,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·Comic World动漫游园会（取消）</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.01.28 09:30-01.28 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>436</v>
+        <v>2223</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>不可售</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -932,12 +932,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78523</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/HAkxl2611705480975408.jpeg</t>
         </is>
       </c>
     </row>
@@ -952,38 +952,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·Comic World动漫游园会（取消）</t>
+          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>剑川路1000号 闵行龙湖天街</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.28 09:30-01.28 17:00</t>
+          <t>2024.01.28 14:00-01.28 20:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2224</v>
+        <v>687</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>不可售</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78523</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/HAkxl2611705480975408.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
         </is>
       </c>
     </row>
@@ -998,38 +998,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
+          <t>上海·次元裂缝-X 新年二次元偶像日</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>剑川路1000号 闵行龙湖天街</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 20:00</t>
+          <t>2024.01.28 14:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>665</v>
+        <v>75</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
         </is>
       </c>
     </row>
@@ -1039,30 +1039,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年二次元偶像日</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 18:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>187</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -1085,30 +1085,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>186</v>
+        <v>739</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -1136,25 +1136,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>701</v>
+        <v>18</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -1182,25 +1182,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1208,12 +1208,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -1228,25 +1228,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>1315</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,30 +1269,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1303</v>
+        <v>19</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,43 +1315,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -1366,38 +1366,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1407,30 +1407,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1438,12 +1438,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -1458,25 +1458,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>1231</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,30 +1499,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1221</v>
+        <v>296</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1545,30 +1545,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>263</v>
+        <v>419</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="H27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ZDx5KYdG1706086833692.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2498</v>
+        <v>2503</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·霓虹次元·二次元夜场3.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 15:30-02.24 21:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ksdMGr6X1706067357226.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1821,30 +1821,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1852,12 +1852,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1867,26 +1867,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,30 +1913,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1964,38 +1964,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -2010,38 +2010,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>882</v>
+        <v>47</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -2051,30 +2051,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>884</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -2097,30 +2097,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>40</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -2143,30 +2143,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -2189,30 +2189,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -2240,25 +2240,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>196</v>
+        <v>11</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -2281,41 +2281,87 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>203</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>13</v>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F42" t="n">
+        <v>14</v>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="H41" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2332,7 +2378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,7 +2502,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2548,11 +2594,11 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>已停售</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -2594,7 +2640,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2640,7 +2686,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2686,7 +2732,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2732,7 +2778,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2778,7 +2824,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2824,7 +2870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2870,7 +2916,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3008,7 +3054,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3100,7 +3146,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3146,7 +3192,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3192,7 +3238,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3238,7 +3284,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>533</v>
+        <v>568</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3330,7 +3376,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3376,7 +3422,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3468,7 +3514,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3514,7 +3560,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3606,7 +3652,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3716,6 +3762,52 @@
       <c r="J30" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024.06.08 19:30-06.08 21:00</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3900,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3900,7 +3992,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3946,7 +4038,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2004</v>
+        <v>2018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3992,7 +4084,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2119</v>
+        <v>2133</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4038,7 +4130,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4084,7 +4176,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>752</v>
+        <v>783</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4176,7 +4268,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4222,7 +4314,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>633</v>
+        <v>783</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4268,7 +4360,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -4314,7 +4406,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -4405,30 +4497,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-01-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·日漫咖啡体验</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>虹桥路1438号高岛屋百货6楼 OASIS书吧</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.01.12 10:00-2024.02.29 22:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>1728</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H2" t="b">
@@ -4436,12 +4528,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202106/okF9H2Uj1623911727887.jpeg</t>
         </is>
       </c>
     </row>
@@ -4451,30 +4543,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>漕宝路3055号 宝龙美术馆</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.11.02 10:00-2024.01.28 18:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>139</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -4482,12 +4574,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
         </is>
       </c>
     </row>
@@ -4497,30 +4589,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
+          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>漕宝路3055号 宝龙美术馆</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.11.02 10:00-2024.01.28 18:00</t>
+          <t>2023.12.01 00:00-2024.01.31 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>2018</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -4528,12 +4620,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
       </c>
     </row>
@@ -4543,26 +4635,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2004</v>
+        <v>2133</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4574,12 +4666,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4589,30 +4681,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2119</v>
+        <v>1686</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -4620,12 +4712,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4635,30 +4727,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1679</v>
+        <v>24</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -4666,12 +4758,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4681,30 +4773,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.31 00:00-2024.01.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>836</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -4712,12 +4804,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
         </is>
       </c>
     </row>
@@ -4727,30 +4819,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>783</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -4758,12 +4850,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4773,30 +4865,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
+          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2023.12.31 00:00-2024.01.29 23:59</t>
+          <t>2024.01.22 14:00-03.03 18:40</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>828</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -4804,12 +4896,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
       </c>
     </row>
@@ -4819,30 +4911,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·25时主题同人茶会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>沪太路3100号 尚大国际</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 12:00-01.27 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>752</v>
+        <v>144</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -4850,12 +4942,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
         </is>
       </c>
     </row>
@@ -4865,43 +4957,43 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·Azurock」Azurose ACG Cover Live</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>愚园路1398号 育音堂音乐公园</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:30</t>
+          <t>2024.01.27 19:00-01.27 21:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
         </is>
       </c>
     </row>
@@ -4916,25 +5008,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·25时主题同人茶会</t>
+          <t>上海·同好召集令火影only</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>沪太路3100号 尚大国际</t>
+          <t>市真南路1199弄1号 智创TOP综合体产城</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.27 18:00</t>
+          <t>2024.01.27 10:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>139</v>
+        <v>560</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -4942,12 +5034,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
         </is>
       </c>
     </row>
@@ -4962,25 +5054,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·Azurock」Azurose ACG Cover Live</t>
+          <t>上海·咒术only-幽暗之森1.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>愚园路1398号 育音堂音乐公园</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.27 19:00-01.27 21:30</t>
+          <t>2024.01.27 10:00-01.27 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>66</v>
+        <v>257</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -4988,12 +5080,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
         </is>
       </c>
     </row>
@@ -5008,38 +5100,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.01.27 13:00-01.28 19:00</t>
+          <t>2024.01.27 15:30-01.27 20:55</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>411</v>
+        <v>34</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/tprwYGIB1705976768947.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
         </is>
       </c>
     </row>
@@ -5054,25 +5146,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>554</v>
+        <v>1204</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>68</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -5080,12 +5172,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -5100,7 +5192,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·咒术only-幽暗之森1.0</t>
+          <t>上海·魔都寒假漫展-CF01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5110,15 +5202,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:00</t>
+          <t>2024.01.27 10:00-01.28 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>252</v>
+        <v>971</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -5126,12 +5218,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
         </is>
       </c>
     </row>
@@ -5146,38 +5238,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.01.27 15:30-01.27 20:55</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>32</v>
+        <v>783</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -5187,30 +5279,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.28 14:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1190</v>
+        <v>442</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -5218,12 +5310,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
         </is>
       </c>
     </row>
@@ -5233,30 +5325,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>957</v>
+        <v>187</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -5264,12 +5356,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -5279,43 +5371,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.01.27 18:30-01.27 21:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>298</v>
+        <v>115</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -5325,30 +5417,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>436</v>
+        <v>26</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -5356,12 +5448,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -5371,43 +5463,43 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>186</v>
+        <v>652</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -5417,43 +5509,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>644</v>
+        <v>739</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -5468,25 +5560,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>701</v>
+        <v>81</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -5494,12 +5586,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -5509,30 +5601,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -5540,12 +5632,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -5555,43 +5647,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>356</v>
+        <v>43</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5693,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5616,11 +5708,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -5632,12 +5724,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -5652,25 +5744,25 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1221</v>
+        <v>12</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -5678,12 +5770,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -5693,30 +5785,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>263</v>
+        <v>1231</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -5724,12 +5816,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -5739,30 +5831,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>117</v>
+        <v>296</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -5770,12 +5862,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -5790,25 +5882,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>419</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>48</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -5816,12 +5908,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/dp013A4p1704783993628.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -5836,21 +5928,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2498</v>
+        <v>61</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -5858,16 +5950,16 @@
         </is>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -5882,38 +5974,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>7</v>
+        <v>2503</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>65</t>
         </is>
       </c>
       <c r="H34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -5923,30 +6015,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>98</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -5954,12 +6046,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5969,30 +6061,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>256</v>
+        <v>11</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -6000,12 +6092,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -6015,26 +6107,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>140</v>
+        <v>259</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6046,12 +6138,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -6061,30 +6153,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -6092,12 +6184,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -6112,38 +6204,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -6158,25 +6250,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>882</v>
+        <v>2</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -6184,12 +6276,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -6199,30 +6291,30 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>43</v>
+        <v>884</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -6230,12 +6322,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -6250,25 +6342,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>380</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -6276,12 +6368,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -6291,30 +6383,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>165</v>
+        <v>11</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -6322,12 +6414,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -6337,30 +6429,30 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -6368,12 +6460,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -6383,43 +6475,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>178</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -6429,43 +6521,43 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>176</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6632,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6586,7 +6678,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,15 +467,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -508,20 +503,15 @@
       <c r="F2" t="n">
         <v>124</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="G2" t="n">
+        <v>139</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
         </is>
@@ -552,22 +542,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>32</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G3" t="n">
+        <v>80</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
@@ -598,22 +583,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1686</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>1694</v>
+      </c>
+      <c r="G4" t="n">
+        <v>55</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
@@ -630,38 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·25时主题同人茶会</t>
+          <t>上海·同好召集令火影only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>沪太路3100号 尚大国际</t>
+          <t>市真南路1199弄1号 智创TOP综合体产城</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.27 18:00</t>
+          <t>2024.01.27 10:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>144</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>575</v>
+      </c>
+      <c r="G5" t="n">
+        <v>88</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
         </is>
       </c>
     </row>
@@ -676,38 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>560</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1237</v>
+      </c>
+      <c r="G6" t="n">
+        <v>98</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -722,7 +692,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·咒术only-幽暗之森1.0</t>
+          <t>上海·魔都寒假漫展-CF01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -732,28 +702,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:00</t>
+          <t>2024.01.27 10:00-01.28 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>257</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>1020</v>
+      </c>
+      <c r="G7" t="n">
+        <v>59</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
         </is>
       </c>
     </row>
@@ -763,43 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.28 14:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1204</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>456</v>
+      </c>
+      <c r="G8" t="n">
+        <v>149</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
         </is>
       </c>
     </row>
@@ -809,43 +769,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海·Comic World动漫游园会（取消）</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.28 09:30-01.28 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>971</v>
+        <v>2218</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78523</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/HAkxl2611705480975408.jpeg</t>
         </is>
       </c>
     </row>
@@ -860,38 +817,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>剑川路1000号 闵行龙湖天街</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.01.28 14:00-01.28 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>442</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>746</v>
+      </c>
+      <c r="G10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
         </is>
       </c>
     </row>
@@ -906,38 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·Comic World动漫游园会（取消）</t>
+          <t>上海·次元裂缝-X 新年二次元偶像日</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.28 09:30-01.28 17:00</t>
+          <t>2024.01.28 14:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2223</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="G11" t="n">
+        <v>70</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78523</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/HAkxl2611705480975408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
         </is>
       </c>
     </row>
@@ -947,43 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>剑川路1000号 闵行龙湖天街</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 20:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>687</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
+        <v>194</v>
+      </c>
+      <c r="G12" t="n">
+        <v>83</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -993,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年二次元偶像日</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1008,28 +950,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 18:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>858</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -1039,43 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>187</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>22</v>
+      </c>
+      <c r="G14" t="n">
+        <v>99</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -1090,38 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>739</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
+        <v>93</v>
+      </c>
+      <c r="G15" t="n">
+        <v>88</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -1136,38 +1063,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>1331</v>
+      </c>
+      <c r="G16" t="n">
+        <v>98</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -1177,43 +1099,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>81</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="G17" t="n">
+        <v>49</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -1223,43 +1140,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1315</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -1269,43 +1181,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>19</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -1320,38 +1227,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
+        <v>101</v>
+      </c>
+      <c r="G20" t="n">
+        <v>49</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -1361,43 +1263,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>96</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="G21" t="n">
+        <v>60</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -1412,38 +1309,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>1251</v>
+      </c>
+      <c r="G22" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1453,43 +1345,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1231</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>351</v>
+      </c>
+      <c r="G23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1499,43 +1386,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>296</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>426</v>
+      </c>
+      <c r="G24" t="n">
+        <v>48</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1432,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1564,24 +1446,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>419</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="G25" t="n">
+        <v>48</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1596,38 +1473,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>117</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="G26" t="n">
+        <v>65</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1642,38 +1514,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>61</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
+        <v>2511</v>
+      </c>
+      <c r="G27" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1688,38 +1555,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2503</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>1</v>
+        <v>509</v>
+      </c>
+      <c r="G28" t="n">
+        <v>98</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1734,38 +1596,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="G29" t="n">
+        <v>49</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1637,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1794,24 +1651,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>11</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>49</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1821,43 +1673,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
+        <v>260</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1867,43 +1714,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>259</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="G32" t="n">
+        <v>60</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1913,43 +1755,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>142</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>60</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1978,22 +1815,17 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>50</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="G34" t="n">
+        <v>70</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
@@ -2024,22 +1856,17 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>47</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="G35" t="n">
+        <v>58</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
@@ -2070,22 +1897,17 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>884</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
+        <v>893</v>
+      </c>
+      <c r="G36" t="n">
+        <v>73</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
@@ -2116,22 +1938,17 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>23</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
+        <v>29</v>
+      </c>
+      <c r="G37" t="n">
+        <v>40</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
@@ -2162,22 +1979,17 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>61</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="G38" t="n">
+        <v>60</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
@@ -2208,22 +2020,17 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>150</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="G39" t="n">
+        <v>80</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
@@ -2254,22 +2061,17 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G40" t="n">
+        <v>70</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
@@ -2300,22 +2102,17 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>203</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="G41" t="n">
+        <v>79</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
@@ -2346,22 +2143,17 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="G42" t="n">
+        <v>89</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2378,7 +2170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2417,15 +2209,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -2458,20 +2245,15 @@
       <c r="F2" t="n">
         <v>24</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+      <c r="G2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
@@ -2502,22 +2284,17 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="G3" t="n">
+        <v>90</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
@@ -2552,18 +2329,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已停售</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+          <t>不可售</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79939</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79939</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/hY6FVnjM1702954652593.jpeg</t>
         </is>
@@ -2575,43 +2349,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.26 19:30-01.26 21:30</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>163</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已停售</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
+        <v>673</v>
+      </c>
+      <c r="G5" t="n">
+        <v>380</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78418</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202311/GHpvkT5Y1699605760230.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2621,43 +2390,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·Azurock」Azurose ACG Cover Live</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>愚园路1398号 育音堂音乐公园</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 19:00-01.27 21:30</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>475</v>
+      </c>
+      <c r="G6" t="n">
+        <v>280</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2667,43 +2431,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 15:30-01.27 20:55</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2713,43 +2472,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海•Risa Yuzuki 1st ONEMAN LIVE 「Future Interlink」 追加公演</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 18:30-01.27 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>299</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>158</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77773</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/XKKYWAk51698315607196.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,43 +2513,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>652</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
+        <v>205</v>
+      </c>
+      <c r="G9" t="n">
+        <v>380</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2805,43 +2554,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>366</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>580</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2851,43 +2595,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>249</v>
+      </c>
+      <c r="G11" t="n">
+        <v>380</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2897,43 +2636,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
         <v>0</v>
       </c>
+      <c r="G12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/dp013A4p1704783993628.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2943,43 +2677,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>201</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>60</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2718,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3004,28 +2733,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>9</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="G14" t="n">
+        <v>380</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -3035,43 +2759,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>245</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -3081,43 +2800,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>643</v>
+      </c>
+      <c r="G16" t="n">
+        <v>480</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -3127,43 +2841,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -3173,43 +2882,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>17</v>
+      </c>
+      <c r="G18" t="n">
+        <v>80</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -3219,43 +2923,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>475</v>
+      </c>
+      <c r="G19" t="n">
+        <v>480</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -3265,43 +2964,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>568</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
         <v>0</v>
       </c>
+      <c r="G20" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -3311,43 +3005,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -3357,43 +3046,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>190</v>
+      </c>
+      <c r="G22" t="n">
+        <v>480</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3403,43 +3087,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>421</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="G23" t="n">
+        <v>80</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3449,43 +3128,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="G24" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3495,43 +3169,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3541,43 +3210,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>178</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>280</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3587,225 +3251,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>10</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>80</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2024-04-13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>丁香路425号 上海东方艺术中心</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>176</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2024-04-20</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2024-04-26</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>东大名路889号 友邦大剧院</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>12</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3822,7 +3297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3861,15 +3336,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -3900,22 +3370,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1728</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>1736</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202106/okF9H2Uj1623911727887.jpeg</t>
         </is>
@@ -3948,20 +3413,15 @@
       <c r="F3" t="n">
         <v>70</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+      <c r="G3" t="n">
+        <v>996</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
@@ -3992,22 +3452,17 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="G4" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
@@ -4038,22 +3493,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>2026</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
@@ -4084,22 +3534,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2133</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>2180</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
@@ -4130,22 +3575,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>836</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+        <v>858</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
         </is>
@@ -4176,22 +3616,17 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>783</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>834</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
@@ -4222,22 +3657,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="G9" t="n">
+        <v>190</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
         </is>
@@ -4270,20 +3700,15 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+      <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
@@ -4314,22 +3739,17 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>783</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>948</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
@@ -4360,22 +3780,17 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>167</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
@@ -4406,22 +3821,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
@@ -4438,7 +3848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4477,15 +3887,10 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>是否有舞台（字符串匹配）</t>
+          <t>Link</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
@@ -4516,22 +3921,17 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1728</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
+        <v>1736</v>
+      </c>
+      <c r="G2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=70666</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202106/okF9H2Uj1623911727887.jpeg</t>
         </is>
@@ -4543,43 +3943,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
+          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>漕宝路3055号 宝龙美术馆</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.11.02 10:00-2024.01.28 18:00</t>
+          <t>2023.12.01 00:00-2024.01.31 23:59</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>124</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="H3" t="b">
-        <v>0</v>
+        <v>2026</v>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
       </c>
     </row>
@@ -4589,43 +3984,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2018</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
+        <v>2180</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4635,43 +4025,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2133</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H5" t="b">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c r="G5" t="n">
+        <v>80</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4700,22 +4085,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1686</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H6" t="b">
-        <v>0</v>
+        <v>1694</v>
+      </c>
+      <c r="G6" t="n">
+        <v>55</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
@@ -4748,20 +4128,15 @@
       <c r="F7" t="n">
         <v>24</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
+      <c r="G7" t="n">
+        <v>90</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
@@ -4792,22 +4167,17 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>836</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
+        <v>858</v>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
         </is>
@@ -4838,22 +4208,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>783</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
+        <v>834</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
@@ -4886,20 +4251,15 @@
       <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H10" t="b">
-        <v>0</v>
+      <c r="G10" t="n">
+        <v>49</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
@@ -4916,38 +4276,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·25时主题同人茶会</t>
+          <t>上海·同好召集令火影only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>沪太路3100号 尚大国际</t>
+          <t>市真南路1199弄1号 智创TOP综合体产城</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.27 12:00-01.27 18:00</t>
+          <t>2024.01.27 10:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>144</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
+        <v>575</v>
+      </c>
+      <c r="G11" t="n">
+        <v>88</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80548</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/dQ4DrxCk1704683144116.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
         </is>
       </c>
     </row>
@@ -4962,38 +4317,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·Azurock」Azurose ACG Cover Live</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>愚园路1398号 育音堂音乐公园</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.27 19:00-01.27 21:30</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
+        <v>1237</v>
+      </c>
+      <c r="G12" t="n">
+        <v>98</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80277</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/5d6O1Rf11703742965244.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -5008,38 +4358,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·魔都寒假漫展-CF01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.27 10:00-01.28 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>560</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H13" t="b">
-        <v>0</v>
+        <v>1020</v>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
         </is>
       </c>
     </row>
@@ -5054,38 +4399,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·咒术only-幽暗之森1.0</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.27 16:00</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>257</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
+        <v>948</v>
+      </c>
+      <c r="G14" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80045</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/hUfcrw3y1703055422885.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -5095,43 +4435,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·日本原版《数码宝贝舞台剧：游乐园之谜》</t>
+          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>茂名南路57号近长乐路 上海兰心大戏院</t>
+          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.01.27 15:30-01.27 20:55</t>
+          <t>2024.01.28 14:00-01.28 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>34</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
+        <v>456</v>
+      </c>
+      <c r="G15" t="n">
+        <v>149</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79783</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/S6nZ327b1702534484951.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
         </is>
       </c>
     </row>
@@ -5141,43 +4476,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>剑川路1000号 闵行龙湖天街</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.28 14:00-01.28 20:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1204</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
+        <v>746</v>
+      </c>
+      <c r="G16" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
         </is>
       </c>
     </row>
@@ -5187,43 +4517,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海·次元裂缝-X 新年二次元偶像日</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.28 14:00-01.28 18:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>971</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="G17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
         </is>
       </c>
     </row>
@@ -5233,43 +4558,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>783</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
+        <v>194</v>
+      </c>
+      <c r="G18" t="n">
+        <v>83</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -5279,43 +4599,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>442</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="H19" t="b">
-        <v>0</v>
+        <v>167</v>
+      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -5325,43 +4640,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>187</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="H20" t="b">
-        <v>0</v>
+        <v>35</v>
+      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -5371,43 +4681,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>115</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H21" t="b">
-        <v>0</v>
+        <v>673</v>
+      </c>
+      <c r="G21" t="n">
+        <v>380</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -5417,43 +4722,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>26</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H22" t="b">
-        <v>0</v>
+        <v>858</v>
+      </c>
+      <c r="G22" t="n">
+        <v>60</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -5463,43 +4763,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>652</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="G23" t="n">
+        <v>99</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -5514,38 +4809,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>739</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
+        <v>93</v>
+      </c>
+      <c r="G24" t="n">
+        <v>88</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -5560,38 +4850,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>81</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
+        <v>1331</v>
+      </c>
+      <c r="G25" t="n">
+        <v>98</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -5601,43 +4886,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>19</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
+        <v>475</v>
+      </c>
+      <c r="G26" t="n">
+        <v>280</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -5647,43 +4927,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="G27" t="n">
+        <v>49</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -5698,38 +4973,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>96</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
+        <v>28</v>
+      </c>
+      <c r="G28" t="n">
+        <v>60</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -5739,43 +5009,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
+        <v>67</v>
+      </c>
+      <c r="G29" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -5785,43 +5050,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1231</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="G30" t="n">
+        <v>49</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -5831,43 +5091,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>296</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -5877,43 +5132,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>419</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
+        <v>1251</v>
+      </c>
+      <c r="G32" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -5923,43 +5173,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>61</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
+        <v>351</v>
+      </c>
+      <c r="G33" t="n">
+        <v>80</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -5974,38 +5219,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2503</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
+        <v>426</v>
+      </c>
+      <c r="G34" t="n">
+        <v>48</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -6020,38 +5260,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="H35" t="b">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="G35" t="n">
+        <v>65</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -6066,38 +5301,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="H36" t="b">
-        <v>0</v>
+        <v>2511</v>
+      </c>
+      <c r="G36" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -6107,43 +5337,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>259</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
+        <v>509</v>
+      </c>
+      <c r="G37" t="n">
+        <v>98</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -6153,43 +5378,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>142</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H38" t="b">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="G38" t="n">
+        <v>49</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -6199,43 +5419,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>49</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -6245,43 +5460,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H40" t="b">
-        <v>0</v>
+        <v>260</v>
+      </c>
+      <c r="G40" t="n">
+        <v>60</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -6291,43 +5501,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>884</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="H41" t="b">
-        <v>0</v>
+        <v>249</v>
+      </c>
+      <c r="G41" t="n">
+        <v>380</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -6337,43 +5542,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>45</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="H42" t="b">
-        <v>0</v>
+        <v>153</v>
+      </c>
+      <c r="G42" t="n">
+        <v>60</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -6383,43 +5583,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H43" t="b">
-        <v>0</v>
+        <v>62</v>
+      </c>
+      <c r="G43" t="n">
+        <v>70</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -6429,12 +5624,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6444,28 +5639,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G44" t="n">
+        <v>60</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+        </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -6475,43 +5665,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>178</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="H45" t="b">
-        <v>0</v>
+        <v>893</v>
+      </c>
+      <c r="G45" t="n">
+        <v>73</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+        </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -6521,43 +5706,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>176</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H46" t="b">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="G46" t="n">
+        <v>80</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+        </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -6567,43 +5747,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>150</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="G47" t="n">
+        <v>50</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -6613,43 +5788,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>11</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="H48" t="b">
-        <v>0</v>
+        <v>178</v>
+      </c>
+      <c r="G48" t="n">
+        <v>80</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -6664,36 +5834,72 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>军工路1076号 纪希片场(秀场)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.02 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>17</v>
+      </c>
+      <c r="G49" t="n">
+        <v>70</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>上海·魔都野良神only</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>南京东路830号 第一百货</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>203</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="H49" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="F50" t="n">
+        <v>209</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,38 +482,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>上海·Hello Kitty Cosmos 50周年光影特展</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>漕宝路3055号 宝龙美术馆</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2023.11.02 10:00-2024.01.28 18:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77862</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202310/QnmD4yOd1698652192047.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -523,38 +523,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>1696</v>
       </c>
       <c r="G3" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·第八届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2024.01.27 10:00-01.28 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1694</v>
+        <v>1239</v>
       </c>
       <c r="G4" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>575</v>
+        <v>194</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1237</v>
+        <v>912</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -687,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1020</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>456</v>
+        <v>105</v>
       </c>
       <c r="G8" t="n">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,40 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·Comic World动漫游园会（取消）</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.28 09:30-01.28 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2218</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1346</v>
+      </c>
+      <c r="G9" t="n">
+        <v>98</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78523</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/HAkxl2611705480975408.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -812,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>剑川路1000号 闵行龙湖天街</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 20:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>746</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>36.9</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -853,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年二次元偶像日</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 18:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -894,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="G12" t="n">
-        <v>83</v>
+        <v>48.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>858</v>
+        <v>106</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -1017,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>1264</v>
       </c>
       <c r="G15" t="n">
-        <v>88</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1331</v>
+        <v>364</v>
       </c>
       <c r="G16" t="n">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1099,38 +1097,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>434</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1140,38 +1138,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>121</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1181,38 +1179,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="G19" t="n">
-        <v>48.8</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1222,38 +1220,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>101</v>
+        <v>2514</v>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>65.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1263,38 +1261,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>511</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1304,38 +1302,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1251</v>
+        <v>11</v>
       </c>
       <c r="G22" t="n">
-        <v>65.90000000000001</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1345,38 +1343,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>351</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1386,38 +1384,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>426</v>
+        <v>264</v>
       </c>
       <c r="G24" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1427,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1468,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1509,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2511</v>
+        <v>73</v>
       </c>
       <c r="G27" t="n">
-        <v>65.8</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1550,38 +1548,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>509</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1591,38 +1589,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>896</v>
       </c>
       <c r="G29" t="n">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1632,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1673,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>260</v>
+        <v>63</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1714,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1753,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1796,38 +1794,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>62</v>
+        <v>215</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -1837,323 +1835,36 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-03-09</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>893</v>
-      </c>
-      <c r="G36" t="n">
-        <v>73</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-03-16</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>29</v>
-      </c>
-      <c r="G37" t="n">
-        <v>40</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-04-05</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>63</v>
-      </c>
-      <c r="G38" t="n">
-        <v>60</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2024-04-27</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>曹杨路1888号 复悦荟</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>149</v>
-      </c>
-      <c r="G39" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>17</v>
-      </c>
-      <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>上海·魔都野良神only</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>南京东路830号 第一百货</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>209</v>
-      </c>
-      <c r="G41" t="n">
-        <v>79</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>16</v>
-      </c>
-      <c r="G42" t="n">
-        <v>89</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2170,7 +1881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2284,7 +1995,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G3" t="n">
         <v>90</v>
@@ -2306,40 +2017,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·沉浸式悬念剧场《9号秘事》</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>人民大道300号 上海大剧院</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.01 19:30-01.28 16:20</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>682</v>
+      </c>
+      <c r="G4" t="n">
+        <v>380</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79939</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/hY6FVnjM1702954652593.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -2349,38 +2058,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>673</v>
+        <v>516</v>
       </c>
       <c r="G5" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2390,38 +2099,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>475</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2431,38 +2140,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2472,38 +2181,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>207</v>
       </c>
       <c r="G8" t="n">
-        <v>158</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,38 +2222,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>205</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2268,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2569,23 +2278,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>253</v>
       </c>
       <c r="G10" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2595,38 +2304,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2350,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2651,23 +2360,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2677,38 +2386,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2718,38 +2427,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2764,33 +2473,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>686</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2805,33 +2514,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>643</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2846,33 +2555,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2882,38 +2591,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>574</v>
       </c>
       <c r="G18" t="n">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2923,38 +2632,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2678,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2979,23 +2688,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -3005,38 +2714,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,38 +2755,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>190</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,38 +2796,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>10</v>
+        <v>179</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3128,38 +2837,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>178</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>80</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,38 +2878,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3210,77 +2919,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="n">
-        <v>80</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3370,7 +3038,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3493,7 +3161,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3534,7 +3202,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2180</v>
+        <v>2197</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3575,7 +3243,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -3616,7 +3284,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>834</v>
+        <v>848</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -3739,7 +3407,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>948</v>
+        <v>990</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3780,7 +3448,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3821,7 +3489,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -3921,7 +3589,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3962,7 +3630,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2026</v>
+        <v>2030</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -4003,7 +3671,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2180</v>
+        <v>2197</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -4085,7 +3753,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -4148,38 +3816,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.31 00:00-2024.01.29 23:59</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>858</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4189,38 +3857,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2023.12.31 00:00-2024.01.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>834</v>
+        <v>859</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
         </is>
       </c>
     </row>
@@ -4230,38 +3898,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.22 14:00-03.03 18:40</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>848</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4271,38 +3939,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·同好召集令火影only</t>
+          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>市真南路1199弄1号 智创TOP综合体产城</t>
+          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 18:00</t>
+          <t>2024.01.22 14:00-03.03 18:40</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>575</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80284</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9xGb6MXN1704183627126.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
       </c>
     </row>
@@ -4331,7 +3999,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="G12" t="n">
         <v>98</v>
@@ -4358,33 +4026,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·魔都寒假漫展-CF01</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 16:00</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1020</v>
+        <v>990</v>
       </c>
       <c r="G13" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/eK96fdcg1703573110264.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4394,38 +4062,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>948</v>
+        <v>194</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -4435,38 +4103,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海 ·WOW潮元原神x星铁主题二次元狂欢派对</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>政通路189号五角场万达广场C栋 元气森林livehouse</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 19:00</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>456</v>
+        <v>179</v>
       </c>
       <c r="G15" t="n">
-        <v>149</v>
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80167</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/QTp32HEM1705028548091.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4476,38 +4144,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第32届动漫节之冬日季</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>剑川路1000号 闵行龙湖天街</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 20:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>746</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>36.9</v>
+        <v>30</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80871</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5fmQrQJ81705573963752.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4517,38 +4185,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年二次元偶像日</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.01.28 14:00-01.28 18:00</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>682</v>
       </c>
       <c r="G17" t="n">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80999</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/lNroHqJY1705549448993.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4558,38 +4226,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>194</v>
+        <v>912</v>
       </c>
       <c r="G18" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4599,38 +4267,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -4640,38 +4308,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -4681,38 +4349,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>673</v>
+        <v>1346</v>
       </c>
       <c r="G21" t="n">
-        <v>380</v>
+        <v>98</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4722,38 +4390,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>858</v>
+        <v>516</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4763,38 +4431,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4804,38 +4472,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4845,38 +4513,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1331</v>
+        <v>77</v>
       </c>
       <c r="G25" t="n">
-        <v>98</v>
+        <v>48.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4886,38 +4554,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>475</v>
+        <v>106</v>
       </c>
       <c r="G26" t="n">
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4927,38 +4595,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4968,38 +4636,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>28</v>
+        <v>1264</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -5009,38 +4677,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>67</v>
+        <v>364</v>
       </c>
       <c r="G29" t="n">
-        <v>48.8</v>
+        <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -5050,38 +4718,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="G30" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -5091,38 +4759,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -5132,12 +4800,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5147,23 +4815,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1251</v>
+        <v>2514</v>
       </c>
       <c r="G32" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -5173,38 +4841,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>351</v>
+        <v>511</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5219,33 +4887,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>426</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5260,33 +4928,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -5296,38 +4964,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2511</v>
+        <v>264</v>
       </c>
       <c r="G36" t="n">
-        <v>65.8</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5337,38 +5005,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>509</v>
+        <v>253</v>
       </c>
       <c r="G37" t="n">
-        <v>98</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5378,38 +5046,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>11</v>
+        <v>155</v>
       </c>
       <c r="G38" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5419,38 +5087,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="G39" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5460,38 +5128,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>260</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5501,38 +5169,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>249</v>
+        <v>896</v>
       </c>
       <c r="G41" t="n">
-        <v>380</v>
+        <v>73</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5542,38 +5210,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153</v>
+        <v>52</v>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5583,38 +5251,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5624,38 +5292,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5665,38 +5333,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>893</v>
+        <v>14</v>
       </c>
       <c r="G45" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5706,38 +5374,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="G46" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5747,38 +5415,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>12</v>
+        <v>179</v>
       </c>
       <c r="G47" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5788,38 +5456,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="G48" t="n">
         <v>80</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5516,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G49" t="n">
         <v>70</v>
@@ -5889,7 +5557,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G50" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1239</v>
+        <v>195</v>
       </c>
       <c r="G4" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>943</v>
       </c>
       <c r="G5" t="n">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>912</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="G7" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>105</v>
+        <v>1354</v>
       </c>
       <c r="G8" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1346</v>
+        <v>46</v>
       </c>
       <c r="G9" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -810,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="G11" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="G12" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -933,38 +933,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -979,33 +979,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>1267</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1264</v>
+        <v>372</v>
       </c>
       <c r="G15" t="n">
-        <v>65.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1056,38 +1056,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>364</v>
+        <v>440</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>434</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1184,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>133</v>
+        <v>2515</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2514</v>
+        <v>511</v>
       </c>
       <c r="G20" t="n">
-        <v>65.8</v>
+        <v>98</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,33 +1266,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>511</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1321,19 +1321,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1343,38 +1343,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>267</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1425,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1512,33 +1512,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1553,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>900</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1589,38 +1589,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>896</v>
+        <v>34</v>
       </c>
       <c r="G29" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1671,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>63</v>
+        <v>152</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>150</v>
+        <v>19</v>
       </c>
       <c r="G32" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1758,33 +1758,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>18</v>
+        <v>219</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,77 +1794,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>215</v>
+        <v>17</v>
       </c>
       <c r="G34" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>17</v>
-      </c>
-      <c r="G35" t="n">
-        <v>89</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1881,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,7 +1995,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2077,7 +2036,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2099,38 +2058,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>532</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2140,38 +2099,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2181,38 +2140,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>207</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>158</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2222,38 +2181,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>207</v>
       </c>
       <c r="G9" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2227,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2278,23 +2237,23 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>253</v>
+        <v>12</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2304,38 +2263,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="G11" t="n">
-        <v>72</v>
+        <v>380</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2309,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2360,23 +2319,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2386,38 +2345,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2427,38 +2386,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2473,33 +2432,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>686</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2514,33 +2473,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>735</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2555,33 +2514,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2591,38 +2550,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>574</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2632,38 +2591,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>50</v>
+        <v>580</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2639,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2688,23 +2649,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2714,38 +2675,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2755,38 +2716,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>192</v>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2796,38 +2757,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>179</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -2837,38 +2798,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="G24" t="n">
         <v>80</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -2878,38 +2839,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -2919,36 +2880,77 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>东大名路889号 友邦大剧院</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2024.04.26 19:30-04.26 21:30</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G26" t="n">
+        <v>280</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+      <c r="G27" t="n">
         <v>80</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3038,7 +3040,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3161,7 +3163,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3202,7 +3204,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2197</v>
+        <v>2209</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3243,7 +3245,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -3284,7 +3286,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -3407,7 +3409,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>990</v>
+        <v>1006</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3448,7 +3450,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3489,7 +3491,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -3589,7 +3591,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3630,7 +3632,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2030</v>
+        <v>2034</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -3671,7 +3673,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2197</v>
+        <v>2209</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -3753,7 +3755,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1696</v>
+        <v>1700</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -3876,7 +3878,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3917,7 +3919,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -3939,38 +3941,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.22 14:00-03.03 18:40</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1006</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -3980,38 +3982,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·第八届次元鹿角动漫游戏展</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>吴中路1588号上海爱琴海购物中心F4 竞梦元宇宙</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.27 10:00-01.28 21:00</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1239</v>
+        <v>195</v>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80979</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/xPOF923U1705545223366.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -4021,38 +4023,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>990</v>
+        <v>187</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4062,38 +4064,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>194</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4103,38 +4105,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>179</v>
+        <v>690</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4144,38 +4146,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>42</v>
+        <v>943</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4185,38 +4187,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>682</v>
+        <v>26</v>
       </c>
       <c r="G17" t="n">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -4231,33 +4233,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>912</v>
+        <v>114</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -4272,33 +4274,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>1354</v>
       </c>
       <c r="G19" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4308,38 +4310,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>532</v>
       </c>
       <c r="G20" t="n">
-        <v>88</v>
+        <v>280</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4349,38 +4351,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1346</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4390,38 +4392,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>516</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4431,38 +4433,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4477,33 +4479,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4513,38 +4515,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4554,38 +4556,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>106</v>
+        <v>1267</v>
       </c>
       <c r="G26" t="n">
-        <v>49</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -4595,38 +4597,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4636,38 +4638,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1264</v>
+        <v>440</v>
       </c>
       <c r="G28" t="n">
-        <v>65.90000000000001</v>
+        <v>48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4677,38 +4679,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="G29" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4723,33 +4725,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>434</v>
+        <v>2515</v>
       </c>
       <c r="G30" t="n">
-        <v>48</v>
+        <v>65.8</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4764,33 +4766,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>133</v>
+        <v>511</v>
       </c>
       <c r="G31" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -4805,33 +4807,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2514</v>
+        <v>11</v>
       </c>
       <c r="G32" t="n">
-        <v>65.8</v>
+        <v>49</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -4846,33 +4848,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>511</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -4882,38 +4884,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>11</v>
+        <v>267</v>
       </c>
       <c r="G34" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -4923,38 +4925,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>254</v>
       </c>
       <c r="G35" t="n">
-        <v>49</v>
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -4964,38 +4966,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>264</v>
+        <v>156</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5005,38 +5007,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>253</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -5046,38 +5048,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5092,33 +5094,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5133,33 +5135,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>900</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5169,38 +5171,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>896</v>
+        <v>53</v>
       </c>
       <c r="G41" t="n">
-        <v>73</v>
+        <v>380</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5215,33 +5217,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G42" t="n">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5251,38 +5253,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G43" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5292,38 +5294,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5333,38 +5335,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>480</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5376,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5389,23 +5391,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G46" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5415,38 +5417,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>179</v>
+        <v>13</v>
       </c>
       <c r="G47" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5477,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G48" t="n">
         <v>80</v>
@@ -5516,7 +5518,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G49" t="n">
         <v>70</v>
@@ -5557,7 +5559,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G50" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G4" t="n">
         <v>83</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
         <v>99</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="G8" t="n">
         <v>98</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="G14" t="n">
         <v>65.90000000000001</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="G15" t="n">
         <v>80</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -1143,33 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·元旦AuPoRo音乐动漫FES</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>141</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1184,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2515</v>
+        <v>156</v>
       </c>
       <c r="G19" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>511</v>
+        <v>2520</v>
       </c>
       <c r="G20" t="n">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,33 +1266,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>511</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,33 +1307,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·霓虹次元·二次元夜场3.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 15:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LTTqrBg91706508336281.jpeg</t>
         </is>
       </c>
     </row>
@@ -1343,38 +1343,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>267</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>156</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1425,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>273</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="G26" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1507,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1553,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>900</v>
+        <v>84</v>
       </c>
       <c r="G28" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1589,38 +1589,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>63</v>
+        <v>902</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1671,38 +1671,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>152</v>
+        <v>38</v>
       </c>
       <c r="G31" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="G33" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,36 +1794,118 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>军工路1076号 纪希片场(秀场)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.02 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>22</v>
+      </c>
+      <c r="G34" t="n">
+        <v>70</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>220</v>
+      </c>
+      <c r="G35" t="n">
+        <v>79</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>17</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F36" t="n">
+        <v>18</v>
+      </c>
+      <c r="G36" t="n">
         <v>89</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1840,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1913,7 +1995,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" t="n">
         <v>90</v>
@@ -1954,10 +2036,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1995,7 +2077,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2036,7 +2118,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2077,7 +2159,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2200,7 +2282,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2241,7 +2323,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
         <v>580</v>
@@ -2282,7 +2364,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2386,12 +2468,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2401,23 +2483,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="G14" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2427,38 +2509,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2473,33 +2555,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>735</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2514,33 +2596,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>80</v>
+        <v>904</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2555,33 +2639,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2591,40 +2675,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>580</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2634,38 +2716,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>50</v>
+        <v>585</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2764,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2690,23 +2774,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2716,38 +2800,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>192</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2757,38 +2841,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2798,38 +2882,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2839,38 +2923,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>147</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2880,38 +2964,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>202</v>
       </c>
       <c r="G26" t="n">
-        <v>280</v>
+        <v>480</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2921,36 +3005,241 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06-08</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G27" t="n">
         <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>丁香路425号 上海东方艺术中心</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2024.04.13 19:30-04.13 21:30</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>182</v>
+      </c>
+      <c r="G28" t="n">
+        <v>80</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-04-20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2024.04.20 19:30-04.20 21:30</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>80</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>东大名路889号 友邦大剧院</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2024.04.26 19:30-04.26 21:30</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>14</v>
+      </c>
+      <c r="G30" t="n">
+        <v>280</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>380</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2024-06-08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.06.08 19:30-06.08 21:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>80</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3040,7 +3329,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3163,7 +3452,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3204,7 +3493,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2209</v>
+        <v>2221</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3245,7 +3534,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="G7" t="n">
         <v>30</v>
@@ -3286,7 +3575,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -3368,7 +3657,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>49</v>
@@ -3409,7 +3698,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1006</v>
+        <v>1037</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3450,7 +3739,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3491,7 +3780,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -3518,7 +3807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3591,7 +3880,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3632,7 +3921,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -3673,7 +3962,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2209</v>
+        <v>2221</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -3714,7 +4003,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
         <v>80</v>
@@ -3755,7 +4044,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -3796,7 +4085,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
         <v>90</v>
@@ -3837,10 +4126,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3878,7 +4167,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3919,7 +4208,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -3960,7 +4249,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1006</v>
+        <v>1037</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4001,7 +4290,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G12" t="n">
         <v>83</v>
@@ -4042,7 +4331,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="G13" t="n">
         <v>30</v>
@@ -4083,7 +4372,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
@@ -4124,7 +4413,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="G15" t="n">
         <v>380</v>
@@ -4165,7 +4454,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>943</v>
+        <v>990</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -4206,7 +4495,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G17" t="n">
         <v>99</v>
@@ -4247,7 +4536,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G18" t="n">
         <v>88</v>
@@ -4288,7 +4577,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1354</v>
+        <v>1371</v>
       </c>
       <c r="G19" t="n">
         <v>98</v>
@@ -4329,7 +4618,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>532</v>
+        <v>554</v>
       </c>
       <c r="G20" t="n">
         <v>280</v>
@@ -4370,7 +4659,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
         <v>49</v>
@@ -4411,7 +4700,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -4452,7 +4741,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G23" t="n">
         <v>48.8</v>
@@ -4493,7 +4782,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G24" t="n">
         <v>49</v>
@@ -4534,7 +4823,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -4575,7 +4864,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1267</v>
+        <v>1280</v>
       </c>
       <c r="G26" t="n">
         <v>65.90000000000001</v>
@@ -4616,7 +4905,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="G27" t="n">
         <v>80</v>
@@ -4657,7 +4946,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -4698,7 +4987,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="G29" t="n">
         <v>65</v>
@@ -4739,7 +5028,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2515</v>
+        <v>2520</v>
       </c>
       <c r="G30" t="n">
         <v>65.8</v>
@@ -4821,7 +5110,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G32" t="n">
         <v>49</v>
@@ -4862,7 +5151,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G33" t="n">
         <v>49</v>
@@ -4903,7 +5192,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -4944,7 +5233,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -4985,7 +5274,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
@@ -5026,7 +5315,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
@@ -5067,7 +5356,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G38" t="n">
         <v>70</v>
@@ -5149,7 +5438,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G40" t="n">
         <v>73</v>
@@ -5190,7 +5479,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G41" t="n">
         <v>380</v>
@@ -5231,7 +5520,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G42" t="n">
         <v>40</v>
@@ -5272,7 +5561,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G43" t="n">
         <v>80</v>
@@ -5313,7 +5602,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G44" t="n">
         <v>50</v>
@@ -5335,38 +5624,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="G45" t="n">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5665,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5391,23 +5680,23 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="G46" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5417,38 +5706,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="G47" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5458,38 +5747,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -5499,38 +5788,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -5545,31 +5834,72 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>军工路1076号 纪希片场(秀场)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.02 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>22</v>
+      </c>
+      <c r="G50" t="n">
+        <v>70</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>上海·魔都野良神only</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>南京东路830号 第一百货</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>219</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="F51" t="n">
+        <v>220</v>
+      </c>
+      <c r="G51" t="n">
         <v>79</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G4" t="n">
         <v>83</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>990</v>
+        <v>1015</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="G8" t="n">
         <v>98</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1280</v>
+        <v>1285</v>
       </c>
       <c r="G14" t="n">
         <v>65.90000000000001</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G15" t="n">
         <v>80</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2520</v>
+        <v>2526</v>
       </c>
       <c r="G20" t="n">
         <v>65.8</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G21" t="n">
         <v>98</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
         <v>148</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G28" t="n">
         <v>70</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="G30" t="n">
         <v>73</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1922,7 +1922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>554</v>
+        <v>564</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" t="n">
         <v>580</v>
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G11" t="n">
         <v>380</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="G14" t="n">
         <v>399</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G15" t="n">
         <v>380</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -2923,38 +2923,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="G25" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,38 +2964,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>202</v>
+        <v>11</v>
       </c>
       <c r="G26" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,38 +3005,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>183</v>
       </c>
       <c r="G27" t="n">
         <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,38 +3046,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>182</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,38 +3087,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3128,38 +3128,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,77 +3169,36 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" t="n">
-        <v>80</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3256,7 +3215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3329,7 +3288,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3493,7 +3452,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2221</v>
+        <v>2226</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3515,38 +3474,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.31 00:00-2024.01.29 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -3556,38 +3515,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·JOYPOLIS世嘉都市乐园</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>中山北路3300号 上海月星环球港</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.21 10:00-02.20 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>865</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
         </is>
       </c>
     </row>
@@ -3597,38 +3556,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-21</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·JOYPOLIS世嘉都市乐园</t>
+          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>中山北路3300号 上海月星环球港</t>
+          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.21 10:00-02.20 21:00</t>
+          <t>2024.01.22 14:00-03.03 18:40</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
       </c>
     </row>
@@ -3638,38 +3597,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.22 14:00-03.03 18:40</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1053</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -3679,38 +3638,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1037</v>
+        <v>213</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -3720,77 +3679,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>204</v>
+        <v>62</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-02-02</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>54</v>
-      </c>
-      <c r="G13" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
@@ -3807,7 +3725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3880,7 +3798,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3902,38 +3820,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.10.16 10:00-2024.10.15 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2037</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>996</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
       </c>
     </row>
@@ -3943,38 +3861,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2221</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>49.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3984,38 +3902,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.01 00:00-2024.01.31 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>2037</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
       </c>
     </row>
@@ -4025,38 +3943,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1701</v>
+        <v>2226</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4066,38 +3984,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4107,38 +4025,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>1703</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4148,38 +4066,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×时光代理人「锦瑟华年主题快闪店」</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023.12.31 00:00-2024.01.29 23:59</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>864</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79972</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/z7bFCMqM1702972063289.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4189,38 +4107,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>865</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4230,38 +4148,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1037</v>
+        <v>870</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4271,38 +4189,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>196</v>
+        <v>1053</v>
       </c>
       <c r="G12" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4312,38 +4230,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -4353,38 +4271,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4399,33 +4317,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>698</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
-        <v>380</v>
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4435,38 +4353,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>990</v>
+        <v>702</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4481,33 +4399,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>28</v>
+        <v>1015</v>
       </c>
       <c r="G17" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4454,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G18" t="n">
         <v>88</v>
@@ -4558,38 +4476,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 19:30-02.04 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1371</v>
+        <v>564</v>
       </c>
       <c r="G19" t="n">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4599,38 +4517,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>554</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4640,38 +4558,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4686,33 +4604,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4727,33 +4645,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G23" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4763,38 +4681,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4809,33 +4727,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>1285</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -4845,38 +4763,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1280</v>
+        <v>408</v>
       </c>
       <c r="G26" t="n">
-        <v>65.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4886,38 +4804,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4850,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4946,19 +4864,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>448</v>
+        <v>123</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4973,33 +4891,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·元旦AuPoRo音乐动漫FES</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -5014,33 +4932,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2520</v>
+        <v>167</v>
       </c>
       <c r="G30" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -5069,7 +4987,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="G31" t="n">
         <v>98</v>
@@ -5192,7 +5110,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -5214,38 +5132,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>258</v>
+        <v>161</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5255,38 +5173,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5296,38 +5214,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>60</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5342,33 +5260,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5383,33 +5301,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>906</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5419,38 +5337,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>902</v>
+        <v>38</v>
       </c>
       <c r="G40" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5460,38 +5378,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G41" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5501,38 +5419,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5542,38 +5460,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>25</v>
+        <v>173</v>
       </c>
       <c r="G43" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5583,38 +5501,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -5624,38 +5542,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="G45" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5665,38 +5583,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>480</v>
+        <v>280</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -5706,38 +5624,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="G47" t="n">
         <v>80</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -5747,38 +5665,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G48" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5788,38 +5706,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="G49" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -5829,79 +5747,38 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>上海·魔都野良神only</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>南京东路830号 第一百货</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>220</v>
-      </c>
-      <c r="G51" t="n">
-        <v>79</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>
       </c>
     </row>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G4" t="n">
         <v>83</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1375</v>
+        <v>1385</v>
       </c>
       <c r="G8" t="n">
         <v>98</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>396</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="G14" t="n">
         <v>65.90000000000001</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="G15" t="n">
         <v>80</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="G20" t="n">
         <v>65.8</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G21" t="n">
         <v>98</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
         <v>148</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
         <v>49</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G28" t="n">
         <v>70</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="G30" t="n">
         <v>73</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>40</v>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>156</v>
+        <v>64</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,38 +1794,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1840,33 +1840,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>223</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1876,36 +1876,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>228</v>
+      </c>
+      <c r="G36" t="n">
+        <v>79</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>19</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F37" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" t="n">
         <v>89</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1922,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,7 +2039,7 @@
         <v>23</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2036,7 +2077,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3" t="n">
         <v>180</v>
@@ -2077,7 +2118,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2118,7 +2159,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2159,7 +2200,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2222,38 +2263,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
-      </c>
-      <c r="G8" t="n">
-        <v>158</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/AJDtxoU21706608146492.jpeg</t>
         </is>
       </c>
     </row>
@@ -2263,38 +2306,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>214</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>158</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2304,38 +2347,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14</v>
+        <v>215</v>
       </c>
       <c r="G10" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2393,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2360,23 +2403,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>262</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2386,38 +2429,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>380</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2475,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,23 +2485,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2468,38 +2511,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>238</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>399</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2552,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2524,23 +2567,23 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>59</v>
+        <v>278</v>
       </c>
       <c r="G15" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2550,38 +2593,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>278</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>399</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2634,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2606,25 +2649,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>910</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="G17" t="n">
+        <v>380</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2680,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2649,23 +2690,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2680,33 +2721,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>26</v>
-      </c>
-      <c r="G19" t="n">
-        <v>80</v>
+        <v>918</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2716,40 +2759,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>589</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>80</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2759,38 +2800,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G21" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2800,38 +2841,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>18</v>
-      </c>
-      <c r="G22" t="n">
-        <v>50</v>
+        <v>591</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2841,38 +2884,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2882,38 +2925,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="G24" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2923,38 +2966,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2964,38 +3007,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>11</v>
+        <v>202</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3048,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3020,23 +3063,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3046,38 +3089,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3087,38 +3130,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>183</v>
       </c>
       <c r="G29" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3128,38 +3171,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3169,36 +3212,118 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>东大名路889号 友邦大剧院</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2024.04.26 19:30-04.26 21:30</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" t="n">
+        <v>280</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>380</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" t="n">
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" t="n">
         <v>80</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3215,7 +3340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3288,7 +3413,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3411,7 +3536,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3452,7 +3577,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2226</v>
+        <v>2242</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3493,7 +3618,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -3616,7 +3741,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3657,7 +3782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3698,7 +3823,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3711,6 +3836,47 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2024.02.15 19:00-03.03 20:10</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>88</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -3725,7 +3891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3798,7 +3964,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3921,7 +4087,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3962,7 +4128,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2226</v>
+        <v>2242</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -4044,7 +4210,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1703</v>
+        <v>1707</v>
       </c>
       <c r="G8" t="n">
         <v>55</v>
@@ -4088,7 +4254,7 @@
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -4126,7 +4292,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
         <v>180</v>
@@ -4167,7 +4333,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
@@ -4208,7 +4374,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1053</v>
+        <v>1076</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -4249,7 +4415,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G13" t="n">
         <v>83</v>
@@ -4290,7 +4456,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G14" t="n">
         <v>30</v>
@@ -4331,7 +4497,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
         <v>30</v>
@@ -4372,7 +4538,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="G16" t="n">
         <v>380</v>
@@ -4413,7 +4579,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1015</v>
+        <v>1062</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -4454,7 +4620,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G18" t="n">
         <v>88</v>
@@ -4495,7 +4661,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>564</v>
+        <v>584</v>
       </c>
       <c r="G19" t="n">
         <v>280</v>
@@ -4536,7 +4702,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
         <v>49</v>
@@ -4577,7 +4743,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -4618,7 +4784,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>89</v>
+        <v>396</v>
       </c>
       <c r="G22" t="n">
         <v>48.8</v>
@@ -4659,7 +4825,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G23" t="n">
         <v>49</v>
@@ -4700,7 +4866,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -4741,7 +4907,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1285</v>
+        <v>1293</v>
       </c>
       <c r="G25" t="n">
         <v>65.90000000000001</v>
@@ -4782,7 +4948,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="G26" t="n">
         <v>80</v>
@@ -4823,7 +4989,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="G27" t="n">
         <v>48</v>
@@ -4864,7 +5030,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
@@ -4905,7 +5071,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
         <v>50</v>
@@ -4946,7 +5112,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -4987,7 +5153,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G31" t="n">
         <v>98</v>
@@ -5028,7 +5194,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G32" t="n">
         <v>49</v>
@@ -5110,7 +5276,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -5151,7 +5317,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G35" t="n">
         <v>60</v>
@@ -5192,7 +5358,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -5274,7 +5440,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>350</v>
       </c>
       <c r="G38" t="n">
         <v>58</v>
@@ -5315,7 +5481,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="G39" t="n">
         <v>73</v>
@@ -5337,38 +5503,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>278</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>399</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5378,38 +5544,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G41" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5419,38 +5585,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5460,38 +5626,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>173</v>
+        <v>19</v>
       </c>
       <c r="G43" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5501,38 +5667,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>63</v>
+        <v>202</v>
       </c>
       <c r="G44" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5850,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -5725,7 +5891,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G49" t="n">
         <v>79</v>
@@ -5747,36 +5913,77 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2024-05-05</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上海·灌篮高手--青春永不散场</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>逸仙路1328弄 新业坊</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024.05.05 10:00-05.05 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>89</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>2024-05-17</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>1</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G51" t="n">
         <v>380</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G4" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1062</v>
+        <v>1091</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G7" t="n">
         <v>88</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1385</v>
+        <v>1393</v>
       </c>
       <c r="G8" t="n">
         <v>98</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
         <v>49</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="G14" t="n">
         <v>65.90000000000001</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G15" t="n">
         <v>80</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
         <v>50</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>354</v>
+        <v>663</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
         <v>148</v>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G28" t="n">
         <v>70</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G29" t="n">
         <v>58</v>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G30" t="n">
         <v>73</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
         <v>40</v>
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="G36" t="n">
         <v>79</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
         <v>89</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" t="n">
         <v>180</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2155,11 +2155,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2196,11 +2196,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="G15" t="n">
         <v>399</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="G16" t="n">
         <v>399</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
         <v>996</v>
@@ -3536,7 +3536,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2038</v>
+        <v>2042</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2242</v>
+        <v>2251</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3618,7 +3618,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3964,7 +3964,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3986,38 +3986,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.12.01 00:00-2024.01.31 23:59</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>2042</v>
       </c>
       <c r="G3" t="n">
-        <v>996</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +4027,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>2251</v>
       </c>
       <c r="G4" t="n">
-        <v>49.9</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +4068,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2038</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,38 +4109,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2242</v>
+        <v>1710</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4150,38 +4150,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4191,38 +4191,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1707</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4232,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>887</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4273,38 +4273,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>1082</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4314,38 +4314,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·寻迹冬日LOVELIVE同好会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>愚园路1250号 新歌空间</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.31 11:30-01.31 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>882</v>
+        <v>201</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
         </is>
       </c>
     </row>
@@ -4355,38 +4355,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1076</v>
+        <v>225</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4396,38 +4396,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4437,38 +4437,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>220</v>
+        <v>709</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4478,38 +4478,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>1091</v>
       </c>
       <c r="G15" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4519,38 +4519,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>706</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -4565,33 +4565,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1062</v>
+        <v>134</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -4606,33 +4606,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>1393</v>
       </c>
       <c r="G18" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4657,11 +4657,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="G19" t="n">
         <v>280</v>
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
         <v>49</v>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G21" t="n">
         <v>60</v>
@@ -4784,7 +4784,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="G22" t="n">
         <v>48.8</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G23" t="n">
         <v>49</v>
@@ -4847,38 +4847,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4893,33 +4893,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1293</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>65.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4929,38 +4929,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>426</v>
+        <v>1295</v>
       </c>
       <c r="G26" t="n">
-        <v>80</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -4970,38 +4970,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -5016,12 +5016,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5030,19 +5030,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>122</v>
+        <v>461</v>
       </c>
       <c r="G28" t="n">
         <v>48</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G29" t="n">
         <v>50</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>354</v>
+        <v>663</v>
       </c>
       <c r="G30" t="n">
         <v>65</v>
@@ -5139,33 +5139,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>515</v>
+        <v>2527</v>
       </c>
       <c r="G31" t="n">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -5180,33 +5180,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>13</v>
+        <v>515</v>
       </c>
       <c r="G32" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5235,19 +5235,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G33" t="n">
         <v>49</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5298,38 +5298,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>164</v>
+        <v>266</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5339,38 +5339,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="G36" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5385,33 +5385,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5426,33 +5426,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>350</v>
+        <v>2</v>
       </c>
       <c r="G38" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5467,33 +5467,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>909</v>
+        <v>353</v>
       </c>
       <c r="G39" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5503,38 +5503,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>278</v>
+        <v>910</v>
       </c>
       <c r="G40" t="n">
-        <v>399</v>
+        <v>73</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5544,38 +5544,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>399</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5585,38 +5585,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G42" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5626,38 +5626,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5667,38 +5667,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>202</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5708,38 +5708,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5749,38 +5749,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G46" t="n">
-        <v>280</v>
+        <v>50</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5790,38 +5790,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="G47" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5831,38 +5831,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="G48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5872,38 +5872,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>228</v>
+        <v>156</v>
       </c>
       <c r="G49" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -5913,38 +5913,38 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·灌篮高手--青春永不散场</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>逸仙路1328弄 新业坊</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G50" t="n">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5954,38 +5954,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>232</v>
       </c>
       <c r="G51" t="n">
-        <v>380</v>
+        <v>79</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>201</v>
+        <v>1123</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -610,33 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1091</v>
+        <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -651,33 +651,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="G6" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>134</v>
+        <v>1398</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1393</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>401</v>
+        <v>128</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>1301</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1295</v>
+        <v>453</v>
       </c>
       <c r="G14" t="n">
-        <v>65.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1015,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>435</v>
+        <v>463</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>461</v>
+        <v>126</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1102,33 +1102,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·元宵AuPoRo音乐动漫FES</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1143,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·元旦AuPoRo音乐动漫FES</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>680</v>
       </c>
       <c r="G18" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1184,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>663</v>
+        <v>2537</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1225,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2527</v>
+        <v>515</v>
       </c>
       <c r="G20" t="n">
-        <v>65.8</v>
+        <v>98</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,33 +1266,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·霓虹次元·二次元夜场3.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 15:30-02.24 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>515</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/LTTqrBg91706508336281.jpeg</t>
         </is>
       </c>
     </row>
@@ -1307,33 +1307,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·霓虹次元·二次元夜场3.0</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 15:30-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LTTqrBg91706508336281.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
         <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>281</v>
       </c>
       <c r="G24" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1425,38 +1425,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>278</v>
+        <v>170</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1466,38 +1466,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1507,38 +1507,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1553,33 +1553,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>94</v>
+        <v>560</v>
       </c>
       <c r="G28" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1594,33 +1594,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>353</v>
+        <v>915</v>
       </c>
       <c r="G29" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1630,38 +1630,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>910</v>
+        <v>44</v>
       </c>
       <c r="G30" t="n">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1676,33 +1676,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G31" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1712,38 +1712,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1753,38 +1753,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1794,38 +1794,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1840,33 +1840,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>238</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -1876,77 +1876,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>232</v>
+        <v>22</v>
       </c>
       <c r="G36" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>21</v>
-      </c>
-      <c r="G37" t="n">
-        <v>89</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2118,7 +2077,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2159,7 +2118,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2200,7 +2159,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2282,7 +2241,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2448,7 +2407,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2530,7 +2489,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>60</v>
@@ -2571,7 +2530,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="G15" t="n">
         <v>399</v>
@@ -2612,7 +2571,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="G16" t="n">
         <v>399</v>
@@ -2653,7 +2612,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G17" t="n">
         <v>380</v>
@@ -2694,7 +2653,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
@@ -2735,7 +2694,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>921</v>
+        <v>926</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2860,7 +2819,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2944,7 +2903,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -3026,7 +2985,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3067,7 +3026,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3149,7 +3108,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
@@ -3231,7 +3190,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -3538,8 +3497,10 @@
       <c r="F5" t="n">
         <v>2042</v>
       </c>
-      <c r="G5" t="n">
-        <v>30</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -3577,7 +3538,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2251</v>
+        <v>2259</v>
       </c>
       <c r="G6" t="n">
         <v>30</v>
@@ -3618,7 +3579,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -3741,7 +3702,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3782,7 +3743,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3823,7 +3784,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G12" t="n">
         <v>30</v>
@@ -3986,38 +3947,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2042</v>
+        <v>2259</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4027,38 +3988,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2251</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4068,38 +4029,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>1711</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4109,38 +4070,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1710</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4111,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4165,23 +4126,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4191,38 +4152,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>895</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4232,38 +4193,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>887</v>
+        <v>1103</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4273,38 +4234,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1082</v>
+        <v>236</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4314,38 +4275,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-01-31</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·寻迹冬日LOVELIVE同好会</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>愚园路1250号 新歌空间</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.01.31 11:30-01.31 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79332</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/Ewreg1JT1701677993728.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4355,38 +4316,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·次元LAB 二次元电音节</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 12:30-02.02 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>225</v>
+        <v>715</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>380</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
         </is>
       </c>
     </row>
@@ -4396,38 +4357,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>1123</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4437,38 +4398,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>709</v>
+        <v>29</v>
       </c>
       <c r="G14" t="n">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -4483,33 +4444,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1091</v>
+        <v>141</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -4524,33 +4485,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>28</v>
+        <v>1398</v>
       </c>
       <c r="G16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4560,38 +4521,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>134</v>
+        <v>605</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>280</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4601,38 +4562,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1393</v>
+        <v>62</v>
       </c>
       <c r="G18" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4642,38 +4603,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>596</v>
+        <v>91</v>
       </c>
       <c r="G19" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4683,38 +4644,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>615</v>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4729,33 +4690,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4765,38 +4726,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>401</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>48.8</v>
+        <v>88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4806,38 +4767,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4847,38 +4808,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·第九届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1301</v>
       </c>
       <c r="G24" t="n">
-        <v>88</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -4888,38 +4849,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
+        <v>453</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4929,38 +4890,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1295</v>
+        <v>463</v>
       </c>
       <c r="G26" t="n">
-        <v>65.90000000000001</v>
+        <v>48</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4970,38 +4931,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·元宵AuPoRo音乐动漫FES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>435</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -5016,33 +4977,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>461</v>
+        <v>681</v>
       </c>
       <c r="G28" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -5057,33 +5018,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·元旦AuPoRo音乐动漫FES</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>2537</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -5098,33 +5059,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>663</v>
+        <v>515</v>
       </c>
       <c r="G30" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5139,33 +5100,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2527</v>
+        <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>65.8</v>
+        <v>49</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5175,38 +5136,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>515</v>
+        <v>281</v>
       </c>
       <c r="G32" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5216,38 +5177,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="G33" t="n">
-        <v>49</v>
+        <v>380</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5257,38 +5218,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>278</v>
+        <v>170</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5298,38 +5259,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>266</v>
+        <v>96</v>
       </c>
       <c r="G35" t="n">
-        <v>380</v>
+        <v>70</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5339,38 +5300,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>166</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>60</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5385,33 +5346,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>94</v>
+        <v>560</v>
       </c>
       <c r="G37" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5426,33 +5387,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>915</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5462,38 +5423,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="G39" t="n">
-        <v>58</v>
+        <v>399</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5503,38 +5464,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>910</v>
+        <v>66</v>
       </c>
       <c r="G40" t="n">
-        <v>73</v>
+        <v>380</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5544,38 +5505,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>291</v>
+        <v>44</v>
       </c>
       <c r="G41" t="n">
-        <v>399</v>
+        <v>40</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5590,33 +5551,33 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5626,38 +5587,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G43" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5667,38 +5628,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5674,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5723,23 +5684,23 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="G45" t="n">
         <v>50</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5749,38 +5710,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>21</v>
+        <v>225</v>
       </c>
       <c r="G46" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5790,38 +5751,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G47" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5811,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G48" t="n">
         <v>80</v>
@@ -5891,7 +5852,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G49" t="n">
         <v>80</v>
@@ -5932,7 +5893,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G50" t="n">
         <v>70</v>
@@ -5973,7 +5934,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G51" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="G13" t="n">
         <v>65.90000000000001</v>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="G14" t="n">
         <v>80</v>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
         <v>50</v>
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="G19" t="n">
         <v>65.8</v>
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
         <v>148</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
         <v>49</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="G29" t="n">
         <v>73</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
         <v>158</v>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="G15" t="n">
         <v>399</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="G16" t="n">
         <v>399</v>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
         <v>380</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
@@ -3299,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3372,7 +3372,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3476,40 +3476,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-01</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·2023《蔚蓝档案》x  萌果酱谷子咖啡</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.01 00:00-2024.01.31 23:59</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2042</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>2261</v>
+      </c>
+      <c r="G5" t="n">
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79005</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/02P8eD3Z1700821985538.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -3519,38 +3517,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2259</v>
+        <v>899</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -3560,38 +3558,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·JOYPOLIS世嘉都市乐园</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>中山北路3300号 上海月星环球港</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.21 10:00-02.20 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>895</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
         </is>
       </c>
     </row>
@@ -3601,38 +3599,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-21</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·JOYPOLIS世嘉都市乐园</t>
+          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>中山北路3300号 上海月星环球港</t>
+          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.21 10:00-02.20 21:00</t>
+          <t>2024.01.22 14:00-03.03 18:40</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81140</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/7Bq5nJNe1705653236022.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
         </is>
       </c>
     </row>
@@ -3642,38 +3640,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·「新春特惠」世嘉都市乐园-JP国潮杂技嘉年华</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>中山北路3300号环球港购物中心4楼 上海世嘉都市乐园</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.22 14:00-03.03 18:40</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1116</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81210</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/sw2khwYM1706086166106.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -3683,38 +3681,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1103</v>
+        <v>241</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -3724,38 +3722,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>236</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -3765,77 +3763,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2024-02-15</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>88</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
@@ -3925,7 +3882,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3966,7 +3923,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -4048,7 +4005,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -4171,7 +4128,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4212,7 +4169,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4253,7 +4210,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4294,7 +4251,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4335,7 +4292,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -4376,7 +4333,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1123</v>
+        <v>1151</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4458,7 +4415,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G15" t="n">
         <v>88</v>
@@ -4499,7 +4456,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="G16" t="n">
         <v>98</v>
@@ -4540,7 +4497,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G17" t="n">
         <v>280</v>
@@ -4581,7 +4538,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
         <v>49</v>
@@ -4622,7 +4579,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -4663,7 +4620,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="G20" t="n">
         <v>48.8</v>
@@ -4786,7 +4743,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -4827,7 +4784,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1301</v>
+        <v>1310</v>
       </c>
       <c r="G24" t="n">
         <v>65.90000000000001</v>
@@ -4868,7 +4825,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="G25" t="n">
         <v>80</v>
@@ -4909,7 +4866,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -4950,7 +4907,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
         <v>50</v>
@@ -4991,7 +4948,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -5032,7 +4989,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="G29" t="n">
         <v>65.8</v>
@@ -5114,7 +5071,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G31" t="n">
         <v>49</v>
@@ -5155,7 +5112,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -5196,7 +5153,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G33" t="n">
         <v>380</v>
@@ -5278,7 +5235,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -5360,7 +5317,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="G37" t="n">
         <v>58</v>
@@ -5401,7 +5358,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="G38" t="n">
         <v>73</v>
@@ -5442,7 +5399,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="G39" t="n">
         <v>399</v>
@@ -5483,7 +5440,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G40" t="n">
         <v>380</v>
@@ -5565,7 +5522,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -5729,7 +5686,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G46" t="n">
         <v>380</v>
@@ -5770,7 +5727,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G47" t="n">
         <v>480</v>
@@ -5811,7 +5768,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G48" t="n">
         <v>80</v>
@@ -5852,7 +5809,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G49" t="n">
         <v>80</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>628</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>128</v>
+        <v>635</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1310</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>65.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -974,38 +974,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第九届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>463</v>
-      </c>
-      <c r="G14" t="n">
-        <v>80</v>
+        <v>1310</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -1015,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="G15" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1063,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1075,19 +1077,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>127</v>
+        <v>468</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1102,33 +1104,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="G17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1143,33 +1145,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>687</v>
-      </c>
-      <c r="G18" t="n">
-        <v>65</v>
+        <v>25</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1184,33 +1188,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2540</v>
+        <v>702</v>
       </c>
       <c r="G19" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>515</v>
+        <v>2548</v>
       </c>
       <c r="G20" t="n">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1266,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·霓虹次元·二次元夜场3.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>万航渡路849号海森国际大厦3楼 Miss Club</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 15:30-02.24 21:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>516</v>
       </c>
       <c r="G21" t="n">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81324</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/LTTqrBg91706508336281.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G22" t="n">
         <v>49</v>
@@ -1403,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1444,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1526,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -1567,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1608,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G29" t="n">
         <v>73</v>
@@ -1690,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1772,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G33" t="n">
         <v>80</v>
@@ -1813,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -1854,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -1895,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -2077,7 +2081,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G4" t="n">
         <v>380</v>
@@ -2118,7 +2122,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2159,7 +2163,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2243,10 +2247,8 @@
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+      <c r="G8" t="n">
+        <v>88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2255,7 +2257,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/AJDtxoU21706608146492.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2409,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2530,7 +2532,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="G15" t="n">
         <v>399</v>
@@ -2571,7 +2573,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="G16" t="n">
         <v>399</v>
@@ -2612,7 +2614,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" t="n">
         <v>380</v>
@@ -2694,7 +2696,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2819,7 +2821,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2903,7 +2905,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -2944,7 +2946,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>80</v>
@@ -2985,7 +2987,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3026,7 +3028,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3108,7 +3110,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
@@ -3372,7 +3374,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3495,7 +3497,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2261</v>
+        <v>2278</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3536,7 +3538,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3659,7 +3661,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3700,7 +3702,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3741,7 +3743,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3882,7 +3884,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3923,7 +3925,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2261</v>
+        <v>2278</v>
       </c>
       <c r="G3" t="n">
         <v>30</v>
@@ -4005,7 +4007,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1712</v>
+        <v>1716</v>
       </c>
       <c r="G5" t="n">
         <v>55</v>
@@ -4128,7 +4130,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4169,7 +4171,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4210,7 +4212,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4251,7 +4253,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4292,7 +4294,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -4333,7 +4335,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1151</v>
+        <v>1181</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4415,7 +4417,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G15" t="n">
         <v>88</v>
@@ -4456,7 +4458,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="G16" t="n">
         <v>98</v>
@@ -4497,7 +4499,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="G17" t="n">
         <v>280</v>
@@ -4538,7 +4540,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
         <v>49</v>
@@ -4579,7 +4581,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
@@ -4620,7 +4622,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="G20" t="n">
         <v>48.8</v>
@@ -4661,7 +4663,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G21" t="n">
         <v>49</v>
@@ -4743,7 +4745,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -4765,38 +4767,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1310</v>
+        <v>471</v>
       </c>
       <c r="G24" t="n">
-        <v>65.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4806,38 +4808,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>463</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -4866,7 +4868,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -4893,33 +4895,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4950,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>687</v>
+        <v>702</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -4989,7 +4991,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2540</v>
+        <v>2548</v>
       </c>
       <c r="G29" t="n">
         <v>65.8</v>
@@ -5030,7 +5032,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G30" t="n">
         <v>98</v>
@@ -5071,7 +5073,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="n">
         <v>49</v>
@@ -5112,7 +5114,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -5153,7 +5155,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G33" t="n">
         <v>380</v>
@@ -5194,7 +5196,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -5235,7 +5237,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -5317,7 +5319,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="G37" t="n">
         <v>58</v>
@@ -5358,7 +5360,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="G38" t="n">
         <v>73</v>
@@ -5399,7 +5401,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="G39" t="n">
         <v>399</v>
@@ -5440,7 +5442,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G40" t="n">
         <v>380</v>
@@ -5522,7 +5524,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -5645,7 +5647,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" t="n">
         <v>50</v>
@@ -5686,7 +5688,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="G46" t="n">
         <v>380</v>
@@ -5727,7 +5729,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G47" t="n">
         <v>480</v>
@@ -5768,7 +5770,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G48" t="n">
         <v>80</v>
@@ -5809,7 +5811,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G49" t="n">
         <v>80</v>
@@ -5850,7 +5852,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G50" t="n">
         <v>70</v>
@@ -5891,7 +5893,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G51" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>99</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G10" t="n">
         <v>60</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>635</v>
+        <v>645</v>
       </c>
       <c r="G11" t="n">
         <v>48.8</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="G15" t="n">
         <v>80</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G16" t="n">
         <v>48</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="G19" t="n">
         <v>65</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G27" t="n">
         <v>70</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G28" t="n">
         <v>58</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G29" t="n">
         <v>73</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
         <v>89</v>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
         <v>180</v>
@@ -2081,10 +2081,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>723</v>
-      </c>
-      <c r="G4" t="n">
-        <v>380</v>
+        <v>728</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2122,7 +2124,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2163,7 +2165,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2409,7 +2411,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2532,7 +2534,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G15" t="n">
         <v>399</v>
@@ -2573,7 +2575,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G16" t="n">
         <v>399</v>
@@ -2696,7 +2698,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2821,7 +2823,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2987,7 +2989,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3028,7 +3030,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3233,7 +3235,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
         <v>380</v>
@@ -3374,7 +3376,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3497,7 +3499,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2278</v>
+        <v>2285</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3538,7 +3540,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3661,7 +3663,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1126</v>
+        <v>1140</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3702,7 +3704,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3743,7 +3745,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3884,7 +3886,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3906,38 +3908,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2278</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>49.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3949,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>2285</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +3990,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1716</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +4031,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>1717</v>
       </c>
       <c r="G6" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,12 +4072,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4085,23 +4087,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4113,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2023.12.27 19:30-2024.02.03 12:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>905</v>
+        <v>57</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4154,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1126</v>
+        <v>914</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4195,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>252</v>
+        <v>1140</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4236,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4280,33 +4282,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>723</v>
+        <v>78</v>
       </c>
       <c r="G12" t="n">
-        <v>380</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4337,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1181</v>
+        <v>1194</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4376,7 +4378,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
         <v>99</v>
@@ -4417,7 +4419,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G15" t="n">
         <v>88</v>
@@ -4458,7 +4460,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="G16" t="n">
         <v>98</v>
@@ -4499,7 +4501,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G17" t="n">
         <v>280</v>
@@ -4540,7 +4542,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G18" t="n">
         <v>49</v>
@@ -4567,33 +4569,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4608,33 +4610,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:30-02.14 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>635</v>
+        <v>106</v>
       </c>
       <c r="G20" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4649,33 +4651,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>132</v>
+        <v>645</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4685,38 +4687,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>132</v>
       </c>
       <c r="G22" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4726,38 +4728,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4767,38 +4769,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>471</v>
+        <v>117</v>
       </c>
       <c r="G24" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4808,38 +4810,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>481</v>
       </c>
       <c r="G25" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4870,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="G26" t="n">
         <v>48</v>
@@ -4950,7 +4952,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="G28" t="n">
         <v>65</v>
@@ -5114,7 +5116,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -5155,7 +5157,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G33" t="n">
         <v>380</v>
@@ -5196,7 +5198,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G34" t="n">
         <v>60</v>
@@ -5237,7 +5239,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G35" t="n">
         <v>70</v>
@@ -5319,7 +5321,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G37" t="n">
         <v>58</v>
@@ -5360,7 +5362,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G38" t="n">
         <v>73</v>
@@ -5401,7 +5403,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="G39" t="n">
         <v>399</v>
@@ -5524,7 +5526,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G42" t="n">
         <v>60</v>
@@ -5688,7 +5690,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G46" t="n">
         <v>380</v>
@@ -5729,7 +5731,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G47" t="n">
         <v>480</v>
@@ -5792,38 +5794,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>163</v>
+        <v>28</v>
       </c>
       <c r="G49" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5838,33 +5840,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="G50" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -5874,38 +5876,38 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>239</v>
+        <v>25</v>
       </c>
       <c r="G51" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
       </c>
     </row>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1194</v>
+        <v>1234</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -815,33 +815,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>106</v>
+        <v>661</v>
       </c>
       <c r="G10" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +856,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>645</v>
+        <v>141</v>
       </c>
       <c r="G11" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,38 +892,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -938,33 +938,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1017,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>481</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>18.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -1058,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1118,19 +1118,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>128</v>
+        <v>472</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1145,35 +1145,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>128</v>
+      </c>
+      <c r="G18" t="n">
+        <v>48</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1188,33 +1186,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>708</v>
-      </c>
-      <c r="G19" t="n">
-        <v>65</v>
+        <v>25</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2548</v>
+        <v>110</v>
       </c>
       <c r="G20" t="n">
-        <v>65.8</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>516</v>
+        <v>727</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1311,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>2552</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>65.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1352,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>517</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>289</v>
+        <v>17</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>174</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,38 +1470,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1511,38 +1511,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,38 +1552,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>567</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1598,33 +1598,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>922</v>
+        <v>111</v>
       </c>
       <c r="G29" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1634,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>568</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>87</v>
+        <v>924</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1757,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1798,38 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>241</v>
+        <v>163</v>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1880,36 +1880,118 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>军工路1076号 纪希片场(秀场)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.02 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>29</v>
+      </c>
+      <c r="G36" t="n">
+        <v>70</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>241</v>
+      </c>
+      <c r="G37" t="n">
+        <v>79</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>25</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="F38" t="n">
+        <v>27</v>
+      </c>
+      <c r="G38" t="n">
         <v>89</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1926,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1999,7 +2081,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2042,8 +2124,10 @@
       <c r="F3" t="n">
         <v>57</v>
       </c>
-      <c r="G3" t="n">
-        <v>180</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2124,7 +2208,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="G5" t="n">
         <v>280</v>
@@ -2165,7 +2249,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="G6" t="n">
         <v>280</v>
@@ -2206,7 +2290,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>80</v>
@@ -2247,7 +2331,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>88</v>
@@ -2329,7 +2413,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2411,7 +2495,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G12" t="n">
         <v>380</v>
@@ -2433,38 +2517,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2563,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2489,23 +2573,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2515,38 +2599,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>389</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>399</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2575,10 +2659,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>389</v>
+        <v>487</v>
       </c>
       <c r="G16" t="n">
-        <v>399</v>
+        <v>699</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2616,7 +2700,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G17" t="n">
         <v>380</v>
@@ -2698,7 +2782,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>933</v>
+        <v>943</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2823,7 +2907,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2907,7 +2991,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
         <v>50</v>
@@ -2989,7 +3073,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="G26" t="n">
         <v>380</v>
@@ -3030,7 +3114,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G27" t="n">
         <v>480</v>
@@ -3052,38 +3136,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,38 +3177,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3134,38 +3218,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G30" t="n">
         <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3175,38 +3259,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="G31" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,38 +3300,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3257,36 +3341,118 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>东大名路889号 友邦大剧院</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024.04.26 19:30-04.26 21:30</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" t="n">
+        <v>280</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
+      <c r="G34" t="n">
+        <v>380</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F35" t="n">
         <v>6</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>80</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3376,7 +3542,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3499,7 +3665,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2285</v>
+        <v>2297</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3540,7 +3706,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3663,7 +3829,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3704,7 +3870,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3745,7 +3911,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3813,7 +3979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3886,7 +4052,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3968,7 +4134,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2285</v>
+        <v>2297</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -4050,7 +4216,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -4091,7 +4257,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
         <v>180</v>
@@ -4113,38 +4279,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>57</v>
+        <v>917</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4154,38 +4320,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>914</v>
+        <v>1150</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4195,38 +4361,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1140</v>
+        <v>274</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4236,38 +4402,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4277,38 +4443,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>78</v>
+        <v>1234</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4323,33 +4489,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·ENP电次元派对vol.04</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>人民大道221号 迪美购物中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.03 18:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1194</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
         </is>
       </c>
     </row>
@@ -4364,33 +4530,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·偶像梦幻祭红白歌合战Only</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 13:30-02.03 22:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="G14" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
         </is>
       </c>
     </row>
@@ -4405,33 +4571,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>149</v>
+        <v>1415</v>
       </c>
       <c r="G15" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4441,38 +4607,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1407</v>
+        <v>625</v>
       </c>
       <c r="G16" t="n">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -4482,38 +4648,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>618</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4523,38 +4689,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4569,33 +4735,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>661</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4610,33 +4776,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:30-02.14 16:30</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4646,38 +4812,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>645</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>48.8</v>
+        <v>88</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4687,38 +4853,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4728,38 +4894,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>499</v>
       </c>
       <c r="G23" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4769,38 +4935,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>117</v>
+        <v>472</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4810,38 +4976,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>481</v>
+        <v>128</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4856,33 +5022,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>472</v>
+        <v>110</v>
       </c>
       <c r="G26" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4897,33 +5063,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>128</v>
+        <v>727</v>
       </c>
       <c r="G27" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4938,33 +5104,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>708</v>
+        <v>2553</v>
       </c>
       <c r="G28" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4979,33 +5145,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2548</v>
+        <v>517</v>
       </c>
       <c r="G29" t="n">
-        <v>65.8</v>
+        <v>98</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5020,33 +5186,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5056,38 +5222,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>17</v>
+        <v>296</v>
       </c>
       <c r="G31" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5102,33 +5268,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5138,38 +5304,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>275</v>
+        <v>177</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5179,38 +5345,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5225,33 +5391,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>108</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5266,33 +5432,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>568</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5307,33 +5473,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>567</v>
+        <v>924</v>
       </c>
       <c r="G37" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5343,38 +5509,38 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>922</v>
+        <v>487</v>
       </c>
       <c r="G38" t="n">
-        <v>73</v>
+        <v>699</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5384,12 +5550,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5399,23 +5565,23 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>389</v>
+        <v>73</v>
       </c>
       <c r="G39" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5430,33 +5596,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="G40" t="n">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5471,33 +5637,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5507,38 +5673,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5548,38 +5714,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5760,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5604,23 +5770,23 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G44" t="n">
         <v>50</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5630,38 +5796,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>25</v>
+        <v>244</v>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5671,38 +5837,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="G46" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5712,12 +5878,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5727,23 +5893,23 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>224</v>
+        <v>188</v>
       </c>
       <c r="G47" t="n">
-        <v>480</v>
+        <v>80</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5753,38 +5919,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="G48" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5799,33 +5965,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>28</v>
+        <v>241</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -5835,77 +6001,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>241</v>
+        <v>27</v>
       </c>
       <c r="G50" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>25</v>
-      </c>
-      <c r="G51" t="n">
-        <v>89</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G11" t="n">
         <v>49</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="G16" t="n">
         <v>80</v>
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="G22" t="n">
         <v>65.8</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
         <v>49</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G29" t="n">
         <v>70</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="G31" t="n">
         <v>73</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G35" t="n">
         <v>80</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G36" t="n">
         <v>70</v>
@@ -1940,7 +1940,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G37" t="n">
         <v>79</v>
@@ -2008,7 +2008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,40 +2146,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·次元LAB 二次元电音节</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中兴路1683号金融街购物中心L3-27 蜚声上海Livehouse</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.02 12:30-02.02 21:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>728</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>636</v>
+      </c>
+      <c r="G4" t="n">
+        <v>280</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80128</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/DEW1XYty1703226993965.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2189,38 +2187,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>625</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2230,38 +2228,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>625</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>280</v>
+        <v>88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2271,38 +2269,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2312,38 +2310,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>216</v>
       </c>
       <c r="G8" t="n">
-        <v>88</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,38 +2351,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>158</v>
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2394,38 +2392,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2435,38 +2433,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2476,38 +2474,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2517,38 +2515,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.08 20:00-03.08 21:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2558,38 +2556,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="G14" t="n">
-        <v>72</v>
+        <v>699</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2599,38 +2597,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2640,38 +2638,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>487</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>699</v>
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2681,12 +2679,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2696,23 +2694,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
-      </c>
-      <c r="G17" t="n">
-        <v>380</v>
+        <v>943</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2737,23 +2737,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2768,35 +2768,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>943</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2806,38 +2804,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>80</v>
+        <v>604</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2847,38 +2847,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2888,40 +2888,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>601</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2931,38 +2929,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2972,38 +2970,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>246</v>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -3013,38 +3011,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>229</v>
       </c>
       <c r="G25" t="n">
-        <v>80</v>
+        <v>480</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3054,38 +3052,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>244</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -3095,38 +3093,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,38 +3134,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3177,38 +3175,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="G29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3218,38 +3216,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3259,38 +3257,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="G31" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3300,38 +3298,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3341,118 +3339,36 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2024-05-17</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>南京西路1376号 上海商城剧院</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" t="n">
-        <v>380</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>6</v>
-      </c>
-      <c r="G35" t="n">
-        <v>80</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3665,7 +3581,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2297</v>
+        <v>2306</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3706,7 +3622,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3829,7 +3745,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3870,7 +3786,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3911,7 +3827,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4134,7 +4050,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2297</v>
+        <v>2306</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -4216,7 +4132,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -4298,7 +4214,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4339,7 +4255,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4380,7 +4296,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4421,7 +4337,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4462,10 +4378,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1234</v>
+        <v>1253</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -4544,10 +4460,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G14" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -4585,7 +4501,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1415</v>
+        <v>1420</v>
       </c>
       <c r="G15" t="n">
         <v>98</v>
@@ -4607,38 +4523,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>625</v>
+        <v>78</v>
       </c>
       <c r="G16" t="n">
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4648,38 +4564,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4694,33 +4610,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>667</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4735,33 +4651,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>661</v>
+        <v>142</v>
       </c>
       <c r="G19" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4771,38 +4687,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4812,38 +4728,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="G21" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4858,33 +4774,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>18.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4829,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
@@ -4954,7 +4870,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
@@ -5036,7 +4952,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -5077,7 +4993,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>727</v>
+        <v>737</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -5200,7 +5116,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G30" t="n">
         <v>49</v>
@@ -5241,7 +5157,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -5282,7 +5198,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G32" t="n">
         <v>380</v>
@@ -5323,7 +5239,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -5364,7 +5280,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -5391,33 +5307,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>569</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5432,33 +5348,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>568</v>
+        <v>926</v>
       </c>
       <c r="G36" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5468,38 +5384,38 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>924</v>
+        <v>495</v>
       </c>
       <c r="G37" t="n">
-        <v>73</v>
+        <v>699</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5425,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5524,23 +5440,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>487</v>
+        <v>73</v>
       </c>
       <c r="G38" t="n">
-        <v>699</v>
+        <v>380</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5555,33 +5471,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="G39" t="n">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5596,33 +5512,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5632,38 +5548,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="G41" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5673,38 +5589,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5635,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5729,23 +5645,23 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G43" t="n">
         <v>50</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5755,38 +5671,38 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>27</v>
+        <v>246</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5796,38 +5712,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="G45" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5837,38 +5753,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>227</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5854,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -5979,7 +5895,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G49" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1253</v>
+        <v>1268</v>
       </c>
       <c r="G4" t="n">
         <v>70</v>
@@ -624,10 +624,12 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G5" t="n">
-        <v>99</v>
+        <v>31</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -665,10 +667,12 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>154</v>
-      </c>
-      <c r="G6" t="n">
-        <v>108</v>
+        <v>158</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -706,7 +710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="G7" t="n">
         <v>98</v>
@@ -747,7 +751,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
         <v>49</v>
@@ -788,7 +792,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -829,7 +833,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="G10" t="n">
         <v>48.8</v>
@@ -870,7 +874,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G11" t="n">
         <v>49</v>
@@ -911,7 +915,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -952,7 +956,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>68</v>
@@ -993,7 +997,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1036,7 +1040,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
         <v>18.8</v>
@@ -1077,7 +1081,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="G16" t="n">
         <v>80</v>
@@ -1118,7 +1122,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G17" t="n">
         <v>48</v>
@@ -1243,7 +1247,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G20" t="n">
         <v>60</v>
@@ -1284,7 +1288,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G21" t="n">
         <v>65</v>
@@ -1325,7 +1329,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2553</v>
+        <v>2560</v>
       </c>
       <c r="G22" t="n">
         <v>65.8</v>
@@ -1448,7 +1452,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>49</v>
@@ -1530,7 +1534,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G27" t="n">
         <v>60</v>
@@ -1571,7 +1575,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -1612,7 +1616,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G29" t="n">
         <v>70</v>
@@ -1653,7 +1657,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G30" t="n">
         <v>58</v>
@@ -1694,7 +1698,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="G31" t="n">
         <v>73</v>
@@ -1735,7 +1739,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G32" t="n">
         <v>40</v>
@@ -1776,7 +1780,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1858,7 +1862,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G35" t="n">
         <v>80</v>
@@ -1940,7 +1944,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G37" t="n">
         <v>79</v>
@@ -1981,7 +1985,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G38" t="n">
         <v>89</v>
@@ -2008,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,40 +2107,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·爱乐汇《天空之城》久石让&amp;宫崎骏动漫经典音乐作品演奏会</t>
+          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.12.27 19:30-2024.02.03 12:00</t>
+          <t>2024.02.04 19:30-02.04 21:30</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>57</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>642</v>
+      </c>
+      <c r="G3" t="n">
+        <v>280</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80103</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/2h2tIq7l1703144874867.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
         </is>
       </c>
     </row>
@@ -2146,38 +2148,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>636</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -2187,38 +2189,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2228,38 +2230,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2269,38 +2271,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2310,38 +2312,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>216</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2358,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2366,23 +2368,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="G9" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2392,38 +2394,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2433,38 +2435,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.08 20:00-03.08 21:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2481,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2489,23 +2491,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2515,38 +2517,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>509</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>399</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2558,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2571,23 +2573,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>495</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>699</v>
+        <v>380</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2597,38 +2599,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="G15" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2643,33 +2645,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>80</v>
+        <v>944</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2684,35 +2688,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>943</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2727,33 +2729,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2763,38 +2765,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>28</v>
-      </c>
-      <c r="G19" t="n">
-        <v>80</v>
+        <v>605</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2804,40 +2808,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>604</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2854,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2862,23 +2864,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2888,38 +2890,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2929,38 +2931,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2970,38 +2972,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G24" t="n">
-        <v>380</v>
+        <v>480</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -3011,38 +3013,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>229</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>480</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3059,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3067,23 +3069,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,38 +3095,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3134,38 +3136,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3175,38 +3177,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,38 +3218,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3257,38 +3259,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3298,77 +3300,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" t="n">
-        <v>80</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3458,7 +3419,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3499,7 +3460,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
         <v>996</v>
@@ -3581,7 +3542,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2306</v>
+        <v>2321</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3622,7 +3583,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3745,7 +3706,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1156</v>
+        <v>1172</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3786,7 +3747,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3827,7 +3788,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3968,7 +3929,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3990,38 +3951,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.10.16 10:00-2024.10.15 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>49.9</v>
+        <v>996</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
       </c>
     </row>
@@ -4031,38 +3992,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2306</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>49.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -4072,38 +4033,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>2321</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4113,38 +4074,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1723</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4154,38 +4115,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>1724</v>
       </c>
       <c r="G7" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4195,38 +4156,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>921</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4236,38 +4197,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1156</v>
+        <v>927</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4277,38 +4238,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>283</v>
+        <v>1172</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4318,38 +4279,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4359,38 +4320,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1253</v>
+        <v>81</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4405,33 +4366,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>1268</v>
       </c>
       <c r="G13" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4446,33 +4407,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>154</v>
+        <v>1423</v>
       </c>
       <c r="G14" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4482,38 +4443,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1420</v>
+        <v>84</v>
       </c>
       <c r="G15" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4523,38 +4484,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4569,33 +4530,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>674</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4610,33 +4571,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>667</v>
+        <v>150</v>
       </c>
       <c r="G18" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4646,38 +4607,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4687,38 +4648,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>165</v>
       </c>
       <c r="G20" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4733,33 +4694,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4749,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>18.8</v>
@@ -4829,7 +4790,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
@@ -4870,7 +4831,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
@@ -4952,7 +4913,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
@@ -4993,7 +4954,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>737</v>
+        <v>751</v>
       </c>
       <c r="G27" t="n">
         <v>65</v>
@@ -5034,7 +4995,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2553</v>
+        <v>2560</v>
       </c>
       <c r="G28" t="n">
         <v>65.8</v>
@@ -5198,7 +5159,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G32" t="n">
         <v>380</v>
@@ -5239,7 +5200,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -5280,7 +5241,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G34" t="n">
         <v>70</v>
@@ -5321,7 +5282,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G35" t="n">
         <v>58</v>
@@ -5362,7 +5323,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="G36" t="n">
         <v>73</v>
@@ -5403,10 +5364,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="G37" t="n">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -5444,7 +5405,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G38" t="n">
         <v>380</v>
@@ -5485,7 +5446,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G39" t="n">
         <v>40</v>
@@ -5526,7 +5487,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G40" t="n">
         <v>60</v>
@@ -5649,7 +5610,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G43" t="n">
         <v>50</v>
@@ -5690,7 +5651,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5731,7 +5692,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G45" t="n">
         <v>480</v>
@@ -5813,7 +5774,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G47" t="n">
         <v>80</v>
@@ -5895,7 +5856,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G49" t="n">
         <v>79</v>
@@ -5936,7 +5897,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G50" t="n">
         <v>89</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G4" t="n">
         <v>70</v>
@@ -610,35 +610,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·ENP电次元派对vol.04</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>人民大道221号 迪美购物中心</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 18:30-02.03 22:00</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>1427</v>
+      </c>
+      <c r="G5" t="n">
+        <v>98</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80945</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/1sjalWS51705479361512.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -648,40 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·偶像梦幻祭红白歌合战Only</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.03 13:30-02.03 22:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>158</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>89</v>
+      </c>
+      <c r="G6" t="n">
+        <v>49</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81199</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/C7E7svbZ1705903245860.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -691,38 +687,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1423</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -732,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>682</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -778,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>157</v>
       </c>
       <c r="G9" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -814,38 +810,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>674</v>
+        <v>173</v>
       </c>
       <c r="G10" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -855,38 +851,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>150</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -901,33 +897,35 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>165</v>
-      </c>
-      <c r="G12" t="n">
-        <v>60</v>
+        <v>1311</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -942,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -978,40 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展（取消）</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1310</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>533</v>
+      </c>
+      <c r="G14" t="n">
+        <v>80</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -1021,38 +1017,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>479</v>
       </c>
       <c r="G15" t="n">
-        <v>18.8</v>
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1062,38 +1058,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>523</v>
+        <v>130</v>
       </c>
       <c r="G16" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1108,33 +1104,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>474</v>
-      </c>
-      <c r="G17" t="n">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1149,33 +1147,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G18" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -1190,35 +1188,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>25</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>757</v>
+      </c>
+      <c r="G19" t="n">
+        <v>65</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1233,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>119</v>
+        <v>2565</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>65.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1274,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>751</v>
+        <v>517</v>
       </c>
       <c r="G21" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1315,33 +1311,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2560</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>65.8</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1356,33 +1352,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>517</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1392,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>18</v>
+        <v>299</v>
       </c>
       <c r="G24" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1433,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1474,38 +1470,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>298</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
         <v>60</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1515,38 +1511,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="G27" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1556,38 +1552,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>571</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1602,33 +1598,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>121</v>
+        <v>931</v>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1638,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>570</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1679,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>929</v>
+        <v>130</v>
       </c>
       <c r="G31" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1720,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G32" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1761,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1802,38 +1798,38 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1843,38 +1839,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>166</v>
+        <v>246</v>
       </c>
       <c r="G35" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -1884,118 +1880,36 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G36" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>上海·魔都野良神only</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>南京东路830号 第一百货</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>244</v>
-      </c>
-      <c r="G37" t="n">
-        <v>79</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>28</v>
-      </c>
-      <c r="G38" t="n">
-        <v>89</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2126,7 +2040,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G3" t="n">
         <v>280</v>
@@ -2290,7 +2204,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2372,7 +2286,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2536,7 +2450,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="G13" t="n">
         <v>399</v>
@@ -2577,7 +2491,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
         <v>380</v>
@@ -2659,7 +2573,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2743,7 +2657,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
@@ -2868,7 +2782,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -2950,7 +2864,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G23" t="n">
         <v>380</v>
@@ -3155,7 +3069,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
@@ -3542,7 +3456,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2321</v>
+        <v>2329</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3583,7 +3497,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3706,7 +3620,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1172</v>
+        <v>1179</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3747,7 +3661,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3788,7 +3702,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3951,38 +3865,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>996</v>
+        <v>49.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3992,38 +3906,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>2329</v>
       </c>
       <c r="G4" t="n">
-        <v>49.9</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4033,38 +3947,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2321</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4074,38 +3988,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>1725</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4115,38 +4029,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1724</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4156,38 +4070,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>938</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4197,38 +4111,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>927</v>
+        <v>1179</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4238,38 +4152,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1172</v>
+        <v>297</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4279,38 +4193,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4320,38 +4234,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·Coser迎春动漫展</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.03 10:00-02.04 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>81</v>
+        <v>1271</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4280,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·第七届次元鹿角二次元派对</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4380,19 +4294,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1268</v>
+        <v>1427</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
         </is>
       </c>
     </row>
@@ -4402,38 +4316,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1423</v>
+        <v>89</v>
       </c>
       <c r="G14" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4443,38 +4357,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4489,33 +4403,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>682</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4530,33 +4444,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>674</v>
+        <v>157</v>
       </c>
       <c r="G17" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4566,38 +4480,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4607,38 +4521,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
       <c r="G19" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4653,33 +4567,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
       <c r="G20" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -4694,33 +4608,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4730,38 +4644,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>12</v>
+        <v>533</v>
       </c>
       <c r="G22" t="n">
-        <v>18.8</v>
+        <v>80</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4771,38 +4685,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>523</v>
+        <v>479</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4817,12 +4731,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4831,19 +4745,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>474</v>
+        <v>130</v>
       </c>
       <c r="G24" t="n">
         <v>48</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4858,33 +4772,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4899,33 +4813,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>119</v>
+        <v>757</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4940,33 +4854,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>751</v>
+        <v>2565</v>
       </c>
       <c r="G27" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4981,33 +4895,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2560</v>
+        <v>517</v>
       </c>
       <c r="G28" t="n">
-        <v>65.8</v>
+        <v>98</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -5022,33 +4936,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>517</v>
+        <v>19</v>
       </c>
       <c r="G29" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5058,38 +4972,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>18</v>
+        <v>299</v>
       </c>
       <c r="G30" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5104,33 +5018,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5140,38 +5054,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>285</v>
+        <v>183</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5181,38 +5095,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>180</v>
+        <v>123</v>
       </c>
       <c r="G33" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5227,33 +5141,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>121</v>
+        <v>571</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5268,33 +5182,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>570</v>
+        <v>931</v>
       </c>
       <c r="G35" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5304,38 +5218,38 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>929</v>
+        <v>515</v>
       </c>
       <c r="G36" t="n">
-        <v>73</v>
+        <v>399</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5345,12 +5259,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5360,23 +5274,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>509</v>
+        <v>79</v>
       </c>
       <c r="G37" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5391,33 +5305,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G38" t="n">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5432,33 +5346,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>47</v>
+        <v>130</v>
       </c>
       <c r="G39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5468,38 +5382,38 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="G40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5442,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
         <v>80</v>
@@ -5610,7 +5524,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G43" t="n">
         <v>50</v>
@@ -5651,7 +5565,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5774,7 +5688,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G47" t="n">
         <v>80</v>
@@ -5815,7 +5729,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -5856,7 +5770,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G49" t="n">
         <v>79</v>
@@ -5897,7 +5811,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G50" t="n">
         <v>89</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1725</v>
+        <v>1732</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -564,38 +564,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1271</v>
+        <v>95</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -605,38 +605,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1427</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -646,38 +646,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
+        <v>695</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -692,33 +692,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="G7" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -728,38 +728,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>682</v>
+        <v>190</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -769,38 +769,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>157</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -815,33 +815,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第九届次元鹿角动漫游戏展（取消）</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 18:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>173</v>
-      </c>
-      <c r="G10" t="n">
-        <v>60</v>
+        <v>1311</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
         </is>
       </c>
     </row>
@@ -856,33 +858,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -892,40 +894,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·第九届次元鹿角动漫游戏展（取消）</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 18:00</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1311</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>554</v>
+      </c>
+      <c r="G12" t="n">
+        <v>80</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80497</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/0duSXTQy1704423309244.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -935,38 +935,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>480</v>
       </c>
       <c r="G13" t="n">
-        <v>18.8</v>
+        <v>48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -976,38 +976,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>533</v>
+        <v>131</v>
       </c>
       <c r="G14" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,33 +1022,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>479</v>
-      </c>
-      <c r="G15" t="n">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1063,33 +1065,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -1104,35 +1106,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>771</v>
+      </c>
+      <c r="G17" t="n">
+        <v>65</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1147,33 +1147,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>126</v>
+        <v>2573</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>65.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1188,33 +1188,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>757</v>
+        <v>517</v>
       </c>
       <c r="G19" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2565</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>65.8</v>
+        <v>49</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,33 +1270,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>517</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>301</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>187</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>299</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1470,38 +1470,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="G26" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1516,33 +1516,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>123</v>
+        <v>937</v>
       </c>
       <c r="G27" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,38 +1552,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>571</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1593,38 +1593,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>931</v>
+        <v>148</v>
       </c>
       <c r="G29" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1634,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>130</v>
+        <v>166</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1757,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,118 +1798,36 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G34" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
-        <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>上海·魔都野良神only</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>南京东路830号 第一百货</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>246</v>
-      </c>
-      <c r="G35" t="n">
-        <v>79</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>29</v>
-      </c>
-      <c r="G36" t="n">
-        <v>89</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1926,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2040,10 +1958,12 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>643</v>
-      </c>
-      <c r="G3" t="n">
-        <v>280</v>
+        <v>648</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -2067,7 +1987,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》（取消）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2083,8 +2003,10 @@
       <c r="F4" t="n">
         <v>7</v>
       </c>
-      <c r="G4" t="n">
-        <v>80</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2103,38 +2025,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>360</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/LywKSi4B1707040250585.png</t>
         </is>
       </c>
     </row>
@@ -2144,38 +2066,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2185,38 +2107,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>218</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>380</v>
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2226,38 +2148,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>219</v>
       </c>
       <c r="G8" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2194,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2282,23 +2204,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2308,38 +2230,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.08 20:00-03.08 21:30</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="G10" t="n">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2349,38 +2271,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2317,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2405,23 +2327,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2431,38 +2353,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>515</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>399</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2394,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2487,23 +2409,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>520</v>
       </c>
       <c r="G14" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2513,38 +2435,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2559,35 +2481,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>947</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2602,33 +2522,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>80</v>
+        <v>951</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2643,33 +2565,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2679,40 +2601,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>605</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2722,38 +2642,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>50</v>
+        <v>605</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2778,23 +2700,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2804,38 +2726,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2845,38 +2767,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>254</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2886,38 +2808,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="G24" t="n">
-        <v>480</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2927,38 +2849,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2895,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2983,23 +2905,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -3009,38 +2931,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3050,38 +2972,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3091,38 +3013,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>190</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3132,38 +3054,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3173,38 +3095,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3214,36 +3136,77 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>380</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>6</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>80</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3333,7 +3296,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3374,7 +3337,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
         <v>996</v>
@@ -3456,7 +3419,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2329</v>
+        <v>2341</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3497,7 +3460,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>938</v>
+        <v>947</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3620,7 +3583,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1179</v>
+        <v>1188</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3661,7 +3624,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3702,7 +3665,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3843,7 +3806,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3865,38 +3828,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.10.16 10:00-2024.10.15 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>49.9</v>
+        <v>996</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
       </c>
     </row>
@@ -3906,38 +3869,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2329</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>49.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3947,38 +3910,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>2341</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -3988,38 +3951,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1725</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4029,38 +3992,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>1732</v>
       </c>
       <c r="G7" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4070,38 +4033,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>938</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4111,38 +4074,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1179</v>
+        <v>947</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4152,38 +4115,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>1188</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4193,38 +4156,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4234,38 +4197,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·Coser迎春动漫展</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1271</v>
+        <v>85</v>
       </c>
       <c r="G12" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80646</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4WVkFc4d1704787729064.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4275,38 +4238,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-03</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·第七届次元鹿角二次元派对</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>长宁路1191号来福士西区(W)B1层01号、11号 星零界</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.03 10:00-02.04 17:00</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1427</v>
+        <v>95</v>
       </c>
       <c r="G13" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79938</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/b1XT2w4T1705027781100.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4316,38 +4279,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4362,33 +4325,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>44</v>
+        <v>695</v>
       </c>
       <c r="G15" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4403,33 +4366,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>682</v>
+        <v>165</v>
       </c>
       <c r="G16" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4439,38 +4402,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4480,38 +4443,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>190</v>
       </c>
       <c r="G18" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4526,33 +4489,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>173</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -4567,33 +4530,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="G20" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4603,38 +4566,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>554</v>
       </c>
       <c r="G21" t="n">
-        <v>18.8</v>
+        <v>80</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4644,38 +4607,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>533</v>
+        <v>480</v>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4653,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4704,19 +4667,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>479</v>
+        <v>131</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4731,33 +4694,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4749,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -4827,7 +4790,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>757</v>
+        <v>771</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -4868,7 +4831,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2565</v>
+        <v>2573</v>
       </c>
       <c r="G27" t="n">
         <v>65.8</v>
@@ -4950,7 +4913,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
         <v>49</v>
@@ -4991,7 +4954,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -5032,7 +4995,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="G31" t="n">
         <v>380</v>
@@ -5073,7 +5036,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -5114,7 +5077,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -5155,7 +5118,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G34" t="n">
         <v>58</v>
@@ -5196,7 +5159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="G35" t="n">
         <v>73</v>
@@ -5237,7 +5200,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="G36" t="n">
         <v>399</v>
@@ -5278,7 +5241,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -5319,7 +5282,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
         <v>40</v>
@@ -5360,7 +5323,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -5401,7 +5364,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
         <v>80</v>
@@ -5442,7 +5405,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G41" t="n">
         <v>80</v>
@@ -5565,7 +5528,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5606,10 +5569,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G45" t="n">
-        <v>480</v>
+        <v>680</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5729,7 +5692,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G48" t="n">
         <v>70</v>
@@ -5770,7 +5733,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="G49" t="n">
         <v>79</v>
@@ -5811,7 +5774,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G50" t="n">
         <v>89</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>695</v>
+        <v>704</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2573</v>
+        <v>2579</v>
       </c>
       <c r="G18" t="n">
         <v>65.8</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G19" t="n">
         <v>98</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G25" t="n">
         <v>70</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G26" t="n">
         <v>58</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="G27" t="n">
         <v>73</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G33" t="n">
         <v>79</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G34" t="n">
         <v>89</v>
@@ -1844,7 +1844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1939,26 +1939,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02-04</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·触手猴钢琴巡演·marasy piano live tour『生音』上海站·Powered by 东方弹幕神乐失落幻想</t>
+          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》（取消）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024.02.04 19:30-02.04 21:30</t>
+          <t>2024.02.14 19:30-02.14 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>648</v>
+        <v>7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80734</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IcjPp0TE1704951328918.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
         </is>
       </c>
     </row>
@@ -1982,40 +1982,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·【情人节特辑】《那年我们》记忆重启韩剧经典OST音乐会《请回答1988》《来自星星的你》（取消）</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024.02.14 19:30-02.14 21:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>381</v>
+      </c>
+      <c r="G4" t="n">
+        <v>360</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80615</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/5DDVhKcO1704767761361.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/LywKSi4B1707040250585.png</t>
         </is>
       </c>
     </row>
@@ -2025,38 +2023,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.20 14:30-02.20 21:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>360</v>
+        <v>88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/LywKSi4B1707040250585.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2066,38 +2064,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2107,38 +2105,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>219</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>380</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2148,38 +2146,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>219</v>
+        <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2192,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2204,23 +2202,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>293</v>
       </c>
       <c r="G9" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2230,38 +2228,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>380</v>
+        <v>90</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2271,38 +2269,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.08 20:00-03.08 21:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2317,7 +2315,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2327,23 +2325,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2353,38 +2351,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>530</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>399</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2392,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2409,23 +2407,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="G14" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2435,38 +2433,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>9</v>
+      </c>
+      <c r="G15" t="n">
         <v>80</v>
       </c>
-      <c r="G15" t="n">
-        <v>380</v>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2481,33 +2479,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>80</v>
+        <v>954</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2522,35 +2522,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>951</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>80</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2565,33 +2563,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2601,38 +2599,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
-      </c>
-      <c r="G19" t="n">
-        <v>80</v>
+        <v>605</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2642,40 +2642,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>605</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>50</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2688,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2700,23 +2698,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2726,38 +2724,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2767,38 +2765,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>265</v>
       </c>
       <c r="G23" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2808,38 +2806,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="G24" t="n">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2849,38 +2847,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>235</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>680</v>
+        <v>50</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2893,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2905,23 +2903,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -2931,38 +2929,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G27" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -2972,38 +2970,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3013,38 +3011,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>190</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3054,38 +3052,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3095,38 +3093,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.17 19:30-05.17 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
         </is>
       </c>
     </row>
@@ -3136,77 +3134,36 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-06-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2024-06-08</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2024.06.08 19:30-06.08 21:00</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" t="n">
-        <v>80</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3296,7 +3253,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3337,7 +3294,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
         <v>996</v>
@@ -3378,7 +3335,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
         <v>49.9</v>
@@ -3419,7 +3376,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2341</v>
+        <v>2352</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3460,7 +3417,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3544,8 +3501,10 @@
       <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>49</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3583,7 +3542,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1188</v>
+        <v>1192</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3624,7 +3583,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3733,7 +3692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3806,7 +3765,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3828,38 +3787,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>996</v>
+        <v>49.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3869,38 +3828,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>2352</v>
       </c>
       <c r="G4" t="n">
-        <v>49.9</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -3910,38 +3869,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2341</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -3951,38 +3910,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>1735</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -3992,38 +3951,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.25 19:30-2024.02.27 21:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1732</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
         </is>
       </c>
     </row>
@@ -4033,38 +3992,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4074,38 +4033,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>947</v>
+        <v>1192</v>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4115,38 +4074,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1188</v>
+        <v>304</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4156,38 +4115,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4197,38 +4156,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4238,38 +4197,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4284,33 +4243,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>704</v>
       </c>
       <c r="G14" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4325,33 +4284,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>695</v>
+        <v>173</v>
       </c>
       <c r="G15" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4361,38 +4320,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>165</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4402,38 +4361,38 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>203</v>
       </c>
       <c r="G17" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4448,33 +4407,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -4489,33 +4448,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4525,38 +4484,38 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>26</v>
+        <v>563</v>
       </c>
       <c r="G20" t="n">
-        <v>18.8</v>
+        <v>80</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4566,38 +4525,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>554</v>
+        <v>485</v>
       </c>
       <c r="G21" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4571,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4626,19 +4585,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>480</v>
+        <v>132</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4653,33 +4612,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="G23" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -4694,33 +4653,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="G24" t="n">
-        <v>158</v>
+        <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4735,33 +4694,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>129</v>
+        <v>777</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4776,33 +4735,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>771</v>
+        <v>2579</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>65.8</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4817,33 +4776,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2573</v>
+        <v>519</v>
       </c>
       <c r="G27" t="n">
-        <v>65.8</v>
+        <v>98</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -4858,33 +4817,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>517</v>
+        <v>22</v>
       </c>
       <c r="G28" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -4894,38 +4853,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>301</v>
       </c>
       <c r="G29" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -4940,33 +4899,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -4976,38 +4935,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5017,38 +4976,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="G32" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5063,33 +5022,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>126</v>
+        <v>576</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -5104,33 +5063,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>575</v>
+        <v>943</v>
       </c>
       <c r="G34" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -5140,38 +5099,38 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>937</v>
+        <v>530</v>
       </c>
       <c r="G35" t="n">
-        <v>73</v>
+        <v>399</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5140,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5196,23 +5155,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>520</v>
+        <v>81</v>
       </c>
       <c r="G36" t="n">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5227,33 +5186,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="G37" t="n">
-        <v>380</v>
+        <v>40</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5268,33 +5227,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>50</v>
+        <v>158</v>
       </c>
       <c r="G38" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5304,38 +5263,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>148</v>
+        <v>9</v>
       </c>
       <c r="G39" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -5350,33 +5309,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G40" t="n">
         <v>80</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5386,38 +5345,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5391,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5442,23 +5401,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="G42" t="n">
         <v>50</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5468,38 +5427,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>31</v>
+        <v>265</v>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5487,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5569,7 +5528,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G45" t="n">
         <v>680</v>
@@ -5673,38 +5632,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
-        <v>70</v>
+        <v>280</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -5719,33 +5678,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>252</v>
+        <v>34</v>
       </c>
       <c r="G49" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5755,36 +5714,77 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>256</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>31</v>
-      </c>
-      <c r="G50" t="n">
+      <c r="F51" t="n">
+        <v>33</v>
+      </c>
+      <c r="G51" t="n">
         <v>89</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="G18" t="n">
         <v>65.8</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>49</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G25" t="n">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="G27" t="n">
         <v>73</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
         <v>40</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1634,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="G31" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>曹杨路1888号 复悦荟</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.27 10:00-04.27 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
         </is>
       </c>
     </row>
@@ -1762,33 +1762,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>256</v>
+        <v>37</v>
       </c>
       <c r="G33" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1798,36 +1798,77 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>261</v>
+      </c>
+      <c r="G34" t="n">
+        <v>79</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
         <v>33</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G35" t="n">
         <v>89</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -1844,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2001,7 +2042,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>381</v>
+        <v>954</v>
       </c>
       <c r="G4" t="n">
         <v>360</v>
@@ -2013,7 +2054,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/LywKSi4B1707040250585.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/wwR8uzxs1707103260934.jpeg</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2124,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
         <v>158</v>
@@ -2124,7 +2165,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
         <v>380</v>
@@ -2206,7 +2247,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G9" t="n">
         <v>380</v>
@@ -2370,7 +2411,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G13" t="n">
         <v>399</v>
@@ -2411,7 +2452,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G14" t="n">
         <v>380</v>
@@ -2493,7 +2534,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2702,7 +2743,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -2784,7 +2825,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G23" t="n">
         <v>380</v>
@@ -2825,7 +2866,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G24" t="n">
         <v>680</v>
@@ -2948,7 +2989,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
         <v>80</v>
@@ -2989,7 +3030,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
@@ -3052,38 +3093,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·冰兔2024线下live《过去和未来》</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>重庆南路308号3楼 上海MAO LIVEHOUSE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.20 13:00-04.20 15:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G30" t="n">
-        <v>280</v>
+        <v>178</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81654</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/OEHnMZmi1706851347869.jpeg</t>
         </is>
       </c>
     </row>
@@ -3093,38 +3134,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3134,36 +3175,77 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>380</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>6</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>80</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3253,7 +3335,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3376,7 +3458,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2352</v>
+        <v>2361</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3417,7 +3499,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3542,7 +3624,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3583,7 +3665,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3624,7 +3706,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3692,7 +3774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3765,7 +3847,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3847,7 +3929,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2352</v>
+        <v>2361</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -3929,7 +4011,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -4011,7 +4093,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4052,7 +4134,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4093,7 +4175,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4134,7 +4216,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4175,7 +4257,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -4216,7 +4298,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4257,7 +4339,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -4298,7 +4380,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -4380,7 +4462,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -4421,7 +4503,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -4462,7 +4544,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G19" t="n">
         <v>18.8</v>
@@ -4503,7 +4585,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="G20" t="n">
         <v>80</v>
@@ -4525,38 +4607,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>485</v>
+        <v>954</v>
       </c>
       <c r="G21" t="n">
-        <v>48</v>
+        <v>360</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/wwR8uzxs1707103260934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4571,12 +4653,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4585,19 +4667,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>487</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4612,33 +4694,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="G23" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -4653,33 +4735,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>135</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -4694,33 +4776,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>777</v>
+        <v>141</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4735,33 +4817,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2579</v>
+        <v>791</v>
       </c>
       <c r="G26" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4776,33 +4858,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>519</v>
+        <v>2583</v>
       </c>
       <c r="G27" t="n">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4817,33 +4899,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>519</v>
       </c>
       <c r="G28" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -4853,38 +4935,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>301</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -4899,33 +4981,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G30" t="n">
-        <v>380</v>
+        <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -4954,7 +5036,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -4995,7 +5077,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -5077,7 +5159,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="G34" t="n">
         <v>73</v>
@@ -5118,7 +5200,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G35" t="n">
         <v>399</v>
@@ -5159,7 +5241,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -5200,7 +5282,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -5241,7 +5323,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -5405,7 +5487,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" t="n">
         <v>50</v>
@@ -5446,7 +5528,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -5487,7 +5569,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5528,7 +5610,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G45" t="n">
         <v>680</v>
@@ -5610,7 +5692,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G47" t="n">
         <v>80</v>
@@ -5632,38 +5714,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G48" t="n">
-        <v>280</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5678,33 +5760,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·魔都野良神only</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京东路830号 第一百货</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.05.01 10:00-05.01 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>34</v>
+        <v>261</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
         </is>
       </c>
     </row>
@@ -5714,77 +5796,36 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>256</v>
+        <v>33</v>
       </c>
       <c r="G50" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2024-05-05</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>上海·灌篮高手--青春永不散场</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>逸仙路1328弄 新业坊</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2024.05.05 10:00-05.05 17:00</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>33</v>
-      </c>
-      <c r="G51" t="n">
-        <v>89</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G13" t="n">
         <v>48</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G16" t="n">
         <v>60</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="G17" t="n">
         <v>65</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="G18" t="n">
         <v>65.8</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G22" t="n">
         <v>60</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G25" t="n">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="G27" t="n">
         <v>73</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G29" t="n">
         <v>60</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G34" t="n">
         <v>79</v>
@@ -1885,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,7 +1958,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
         <v>180</v>
@@ -2042,10 +2042,12 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>954</v>
-      </c>
-      <c r="G4" t="n">
-        <v>360</v>
+        <v>994</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -2064,38 +2066,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·天空之城-经典动漫烛光音乐会</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2024.02.23 19:30-02.23 21:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>88</v>
+        <v>994</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/wwR8uzxs1707103260934.jpeg</t>
         </is>
       </c>
     </row>
@@ -2105,38 +2109,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·天空之城-经典动漫烛光音乐会</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.23 19:30-02.23 21:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81541</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/Q3L80ixO1706778157039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2146,38 +2150,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·青山吉能见面会</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.02.25 14:30-02.25 19:30</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>380</v>
+        <v>158</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -2187,38 +2191,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·2024藤田玲上海粉丝见面会</t>
+          <t>上海·青山吉能见面会</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>虹许路731号4号楼 THE BOXX•城市乐园</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.03.02 12:30-03.02 19:40</t>
+          <t>2024.02.25 14:30-02.25 19:30</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>220</v>
       </c>
       <c r="G8" t="n">
-        <v>580</v>
+        <v>380</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80142</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/1npuHFBM1703231674558.jpeg</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2237,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·小山百代2024上海粉丝见面会</t>
+          <t>上海·2024藤田玲上海粉丝见面会</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2243,23 +2247,23 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.03.02 13:00-03.02 20:00</t>
+          <t>2024.03.02 12:30-03.02 19:40</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>295</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>380</v>
+        <v>580</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80993</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Vm6ntgVd1705548188785.png</t>
         </is>
       </c>
     </row>
@@ -2269,38 +2273,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.03.08 20:00-03.08 21:30</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="G10" t="n">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -2310,38 +2314,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
+          <t>上海·《月亮代表我的心》摇滚情歌之夜--630乐团演绎经典</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>淞沪路388号创智天地广场7号楼一层 创智天地梦剧场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.03.09 19:30-03.09 21:00</t>
+          <t>2024.03.08 20:00-03.08 21:30</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81676</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/0yMuaTCo1706860617422.png</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2360,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·爱乐之城音乐会</t>
+          <t>上海·《挪威的森林》—摇滚情歌之夜演唱会</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2366,23 +2370,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.03.09 14:00-03.09 15:30</t>
+          <t>2024.03.09 19:30-03.09 21:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81241</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/1FJ0Fj5m1705915336335.jpeg</t>
         </is>
       </c>
     </row>
@@ -2392,38 +2396,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-03-10</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·三森铃子10周年纪念2024演唱会</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.03.10 18:00-03.10 19:30</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>535</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>399</v>
+        <v>60</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2437,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2448,23 +2452,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>83</v>
+        <v>546</v>
       </c>
       <c r="G14" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -2474,38 +2478,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -2520,35 +2524,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.03.17 18:00-03.17 19:30</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>956</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>80</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -2563,33 +2565,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
+          <t>上海·amazarashi Asia Tour 2024 「永遠市 -Eternal City-」上海公演</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.03.17 19:30-03.17 21:00</t>
+          <t>2024.03.17 18:00-03.17 19:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>80</v>
+        <v>961</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81039</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/icsawZU11705566039011.jpeg</t>
         </is>
       </c>
     </row>
@@ -2604,33 +2608,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海·《笑傲江湖》经典武侠影视金曲音乐会</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 19:30-03.17 21:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80875</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/8AwIAy4I1705385447242.jpeg</t>
         </is>
       </c>
     </row>
@@ -2640,40 +2644,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·春卷饭 十周年  2024  专场演出</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.03.21 20:00-03.21 22:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>605</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>已售罄</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>80</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -2683,38 +2685,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·春卷饭 十周年  2024  专场演出</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>嘉兴路街道瑞虹路188号瑞虹天地月亮湾3层 Modern Sky LAB摩登天空(瑞虹天地店)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.21 20:00-03.21 22:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>50</v>
+        <v>606</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81190</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/ho9rIMg21705894649801.jpeg</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2733,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2739,23 +2743,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -2765,38 +2769,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.24 19:30-03.24 21:00</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -2806,38 +2810,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·“燃魂巅峰交响版”VICTORY·星球大战·加勒比海盗 大型交响音乐会</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>丁香路425号(上海科技馆地铁站1号口步行460米) 上海东方艺术中心音乐厅</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.24 19:30-03.24 21:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>268</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>380</v>
+        <v>80</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81501</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IEM4vSmT1706520953088.jpeg</t>
         </is>
       </c>
     </row>
@@ -2847,38 +2851,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="G24" t="n">
-        <v>680</v>
+        <v>380</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -2888,38 +2892,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>238</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2944,23 +2948,23 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -2970,38 +2974,38 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3011,38 +3015,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
         <v>80</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3052,38 +3056,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3098,33 +3102,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·冰兔2024线下live《过去和未来》</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>重庆南路308号3楼 上海MAO LIVEHOUSE</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.20 13:00-04.20 15:00</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81654</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/OEHnMZmi1706851347869.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3134,38 +3138,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·冰兔2024线下live《过去和未来》</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>重庆南路308号3楼 上海MAO LIVEHOUSE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.20 13:00-04.20 15:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>80</v>
       </c>
       <c r="G31" t="n">
-        <v>280</v>
+        <v>178</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81654</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/OEHnMZmi1706851347869.jpeg</t>
         </is>
       </c>
     </row>
@@ -3175,38 +3179,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.26 19:30-04.26 21:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
-        <v>380</v>
+        <v>280</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
         </is>
       </c>
     </row>
@@ -3216,36 +3220,77 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>380</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>6</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G34" t="n">
         <v>80</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3335,7 +3380,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3458,7 +3503,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2361</v>
+        <v>2369</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3499,7 +3544,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3624,7 +3669,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3665,7 +3710,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3774,7 +3819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3847,7 +3892,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3869,38 +3914,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.10.16 10:00-2024.10.15 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>49.9</v>
+        <v>996</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
         </is>
       </c>
     </row>
@@ -3910,38 +3955,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2361</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>30</v>
+        <v>49.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -3951,38 +3996,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>36</v>
+        <v>2369</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -3992,38 +4037,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1737</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4033,38 +4078,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-25</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·爱乐汇“浪漫经典·一生必听”永恒精选2023烛光音乐会</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.25 19:30-2024.02.27 21:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>1737</v>
       </c>
       <c r="G7" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/AeWGG9Rk1703131189224.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4138,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4134,7 +4179,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1197</v>
+        <v>1206</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4175,7 +4220,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4257,7 +4302,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -4298,7 +4343,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4339,7 +4384,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -4380,7 +4425,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -4462,7 +4507,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -4503,7 +4548,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -4544,7 +4589,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
         <v>18.8</v>
@@ -4585,7 +4630,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="G20" t="n">
         <v>80</v>
@@ -4626,10 +4671,12 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>954</v>
-      </c>
-      <c r="G21" t="n">
-        <v>360</v>
+        <v>994</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -4667,7 +4714,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
@@ -4708,7 +4755,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -4790,7 +4837,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -4831,7 +4878,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>791</v>
+        <v>801</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -4872,7 +4919,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="G27" t="n">
         <v>65.8</v>
@@ -4995,7 +5042,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -5036,7 +5083,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -5077,7 +5124,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -5159,7 +5206,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="G34" t="n">
         <v>73</v>
@@ -5200,7 +5247,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="G35" t="n">
         <v>399</v>
@@ -5323,7 +5370,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -5528,7 +5575,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -5569,7 +5616,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5610,7 +5657,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G45" t="n">
         <v>680</v>
@@ -5632,38 +5679,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
         </is>
       </c>
     </row>
@@ -5673,38 +5720,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>191</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -5714,38 +5761,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>37</v>
+        <v>191</v>
       </c>
       <c r="G48" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5760,33 +5807,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>261</v>
+        <v>37</v>
       </c>
       <c r="G49" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5796,36 +5843,77 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>266</v>
+      </c>
+      <c r="G50" t="n">
+        <v>79</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>33</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G51" t="n">
         <v>89</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>1034</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -940,33 +940,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·  第五十三届妖漫动漫游戏展</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>漕溪北路339号百脑汇4楼 百脑汇</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>488</v>
+        <v>166</v>
       </c>
       <c r="G13" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/MVRgtEd91707208495928.jpeg</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -995,19 +995,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>133</v>
+        <v>490</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -1022,35 +1022,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
+          <t>上海·SISP动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
+          <t>年家浜路518号 周浦万达广场</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.24 08:00-02.24 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>134</v>
+      </c>
+      <c r="G15" t="n">
+        <v>48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
         </is>
       </c>
     </row>
@@ -1065,33 +1063,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·元宵AuPoRo音乐动漫FES（取消）</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>友谊路街道友谊路318号 灏唯滨江智创园</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 08:00-02.24 21:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>144</v>
-      </c>
-      <c r="G16" t="n">
-        <v>60</v>
+        <v>26</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81481</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/w4kr4a0X1706497345456.jpeg</t>
         </is>
       </c>
     </row>
@@ -1106,33 +1106,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>801</v>
+        <v>152</v>
       </c>
       <c r="G17" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -1147,33 +1147,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2585</v>
+        <v>808</v>
       </c>
       <c r="G18" t="n">
-        <v>65.8</v>
+        <v>65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -1188,33 +1188,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>519</v>
+        <v>2588</v>
       </c>
       <c r="G19" t="n">
-        <v>98</v>
+        <v>65.8</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -1229,33 +1229,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>520</v>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·魔都多厨狂喜漫展-CH01</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
         <v>49</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -1306,38 +1306,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·魔都多厨狂喜漫展-CH01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81423</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/axpOY3zo1706173660010.jpeg</t>
         </is>
       </c>
     </row>
@@ -1347,38 +1347,38 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>195</v>
+        <v>306</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -1388,38 +1388,38 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>浦锦南路1586弄2号 奇迹花园</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.03.08 10:00-03.10 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>198</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -1429,38 +1429,38 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第八届ACBC动漫盛典-国潮汉服游园会</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>浦锦南路1586弄2号 奇迹花园</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.08 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="G25" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81456</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/qZtpawf51706254849667.jpeg</t>
         </is>
       </c>
     </row>
@@ -1475,33 +1475,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>周家嘴路3608号 宝龙旭辉广场</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.09 10:20-03.10 16:30</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>576</v>
+        <v>144</v>
       </c>
       <c r="G26" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -1516,33 +1516,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
+          <t>上海·第五十三届燃梦星辰动漫嘉年华-随机宅舞</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>漕宝路1688号 诺宝中心酒店</t>
+          <t>周家嘴路3608号 宝龙旭辉广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.09 16:30</t>
+          <t>2024.03.09 10:20-03.10 16:30</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>950</v>
+        <v>579</v>
       </c>
       <c r="G27" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80571</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/SHH70VXN1704700240858.jpeg</t>
         </is>
       </c>
     </row>
@@ -1552,38 +1552,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·青山刚昌ONLY【名侦探柯南&amp;魔术快斗】</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>漕宝路1688号 诺宝中心酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.09 10:00-03.09 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>952</v>
       </c>
       <c r="G28" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=76410</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202309/fVXMrcHy1693971682397.jpeg</t>
         </is>
       </c>
     </row>
@@ -1598,33 +1598,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1634,38 +1634,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·首届Redamancy动漫游戏嘉年华</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>198</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>68</v>
+        <v>1011</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-27</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·  第五十三届妖漫动漫游戏展</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>曹杨路1888号 复悦荟</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.27 10:00-04.27 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="G32" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78657</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/tamNdgEN1705331335847.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G34" t="n">
         <v>79</v>
@@ -1885,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="G14" t="n">
         <v>399</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
         <v>380</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>50</v>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G25" t="n">
         <v>680</v>
@@ -2933,38 +2933,38 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·RAISE A SUILEN ASIA TOUR 2024 IN SHANGHAI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>中山南二路857-859号 宛平剧院</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.30 19:00-03.31 19:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1545</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>780</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81777</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/wNFwwhKK1707188320465.jpeg</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2989,23 +2989,23 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.03.31 15:00-03.31 16:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -3015,38 +3015,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
+          <t>上海·《热血之巅·突破次元壁》ACG动漫电影音乐会</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.04.06 19:30-04.06 21:30</t>
+          <t>2024.03.31 15:00-03.31 16:30</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81672</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/5k9iIwRO1706859635834.jpeg</t>
         </is>
       </c>
     </row>
@@ -3056,38 +3056,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·从Butter-Fly到夏目之爱してる —— “好想大声说爱你”动漫钢琴演奏会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>复兴中路1380号 捷豹上海交响音乐厅</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.04.06 19:30-04.06 21:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80050</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202312/0iJP3TY61703056498448.jpeg</t>
         </is>
       </c>
     </row>
@@ -3097,38 +3097,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-04-20</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.04.20 19:30-04.20 21:30</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>191</v>
       </c>
       <c r="G30" t="n">
         <v>80</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -3143,33 +3143,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·冰兔2024线下live《过去和未来》</t>
+          <t>上海· 茅原实里动漫交响音乐会</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>重庆南路308号3楼 上海MAO LIVEHOUSE</t>
+          <t>东大名路889号 友邦大剧院</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.04.20 13:00-04.20 15:00</t>
+          <t>2024.04.20 19:30-04.20 21:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>178</v>
+        <v>280</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81654</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81703</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/OEHnMZmi1706851347869.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/yiVaqJVK1707016321221.jpeg</t>
         </is>
       </c>
     </row>
@@ -3179,38 +3179,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+          <t>上海·Laurent Coulondre“心动巴黎”2024中国巡回音乐会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>东大名路889号 友邦大剧院</t>
+          <t>汾阳路20号上海音乐学院内 上海贺绿汀音乐厅</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.26 19:30-04.26 21:30</t>
+          <t>2024.04.20 19:30-04.20 21:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
-        <v>280</v>
+        <v>80</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81135</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/wXDdS5ap1705651730828.jpeg</t>
         </is>
       </c>
     </row>
@@ -3220,38 +3220,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-20</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+          <t>上海·冰兔2024线下live《过去和未来》</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>重庆南路308号3楼 上海MAO LIVEHOUSE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.17 19:30-05.17 21:00</t>
+          <t>2024.04.20 13:00-04.20 15:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="G33" t="n">
-        <v>380</v>
+        <v>178</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81654</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/OEHnMZmi1706851347869.jpeg</t>
         </is>
       </c>
     </row>
@@ -3261,36 +3261,118 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>上海· 夏川里美 2024 巡回演唱会 出道 25 周年纪念专场</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>东大名路889号 友邦大剧院</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2024.04.26 19:30-04.26 21:30</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>24</v>
+      </c>
+      <c r="G34" t="n">
+        <v>280</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81139</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/0Fj4cYOH1705652393930.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024-05-17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上海·Rie fu 船越里惠 日本知名唱作歌手2024出道20周年中国巡回演唱会</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>南京西路1376号 上海商城剧院</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.05.17 19:30-05.17 21:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>380</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=81506</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/6ue4xoaR1706523724335.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>2024-06-08</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>上海·菊次郎的夏天——久石让钢琴曲梦幻之旅演奏会</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2024.06.08 19:30-06.08 21:00</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>6</v>
-      </c>
-      <c r="G34" t="n">
+      <c r="F36" t="n">
+        <v>7</v>
+      </c>
+      <c r="G36" t="n">
         <v>80</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=81413</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>//i2.hdslb.com/bfs/openplatform/202401/QqKuy4611706169245363.jpeg</t>
         </is>
@@ -3380,7 +3462,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3503,7 +3585,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3544,7 +3626,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3669,7 +3751,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3710,7 +3792,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3751,7 +3833,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3892,7 +3974,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -4015,7 +4097,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -4097,7 +4179,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="G7" t="n">
         <v>55</v>
@@ -4138,7 +4220,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -4179,7 +4261,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1206</v>
+        <v>1221</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4220,7 +4302,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4261,7 +4343,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4302,7 +4384,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G12" t="n">
         <v>49</v>
@@ -4343,7 +4425,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>348</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -4384,7 +4466,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="G14" t="n">
         <v>48.8</v>
@@ -4425,7 +4507,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G15" t="n">
         <v>49</v>
@@ -4507,7 +4589,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -4548,7 +4630,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>21</v>
+        <v>1034</v>
       </c>
       <c r="G18" t="n">
         <v>68</v>
@@ -4589,7 +4671,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
         <v>18.8</v>
@@ -4630,7 +4712,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="G20" t="n">
         <v>80</v>
@@ -4671,7 +4753,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>994</v>
+        <v>1017</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -4714,7 +4796,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G22" t="n">
         <v>48</v>
@@ -4755,7 +4837,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G23" t="n">
         <v>48</v>
@@ -4837,7 +4919,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -4878,7 +4960,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="G26" t="n">
         <v>65</v>
@@ -4919,7 +5001,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="G27" t="n">
         <v>65.8</v>
@@ -4960,7 +5042,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G28" t="n">
         <v>98</v>
@@ -5042,7 +5124,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -5083,7 +5165,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -5124,7 +5206,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G32" t="n">
         <v>70</v>
@@ -5165,7 +5247,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -5206,7 +5288,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="G34" t="n">
         <v>73</v>
@@ -5247,7 +5329,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="G35" t="n">
         <v>399</v>
@@ -5288,7 +5370,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G36" t="n">
         <v>380</v>
@@ -5329,7 +5411,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G37" t="n">
         <v>40</v>
@@ -5370,7 +5452,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G38" t="n">
         <v>60</v>
@@ -5452,7 +5534,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G40" t="n">
         <v>80</v>
@@ -5493,7 +5575,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
         <v>50</v>
@@ -5575,7 +5657,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G43" t="n">
         <v>380</v>
@@ -5616,7 +5698,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5657,7 +5739,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="G45" t="n">
         <v>680</v>
@@ -5698,7 +5780,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>1011</v>
       </c>
       <c r="G46" t="n">
         <v>60</v>
@@ -5821,7 +5903,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G49" t="n">
         <v>70</v>
@@ -5862,7 +5944,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G50" t="n">
         <v>79</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1034</v>
+        <v>1052</v>
       </c>
       <c r="G9" t="n">
         <v>68</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>46</v>
+        <v>346</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G13" t="n">
         <v>80</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="G19" t="n">
         <v>65.8</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G28" t="n">
         <v>73</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G33" t="n">
         <v>70</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G34" t="n">
         <v>79</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1017</v>
+        <v>1027</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
         <v>88</v>
@@ -2210,7 +2210,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>60</v>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="G14" t="n">
         <v>399</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G25" t="n">
         <v>680</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1545</v>
+        <v>2425</v>
       </c>
       <c r="G26" t="n">
         <v>780</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -3239,7 +3239,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G33" t="n">
         <v>178</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2379</v>
+        <v>2390</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3996,38 +3996,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>上海·古影文化《1941·新和医院》大型沉浸式互动剧场</t>
+          <t>上海·方块大战（豫园店）</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>金玉路2号 古影沉浸式互动游戏剧场</t>
+          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2023.10.16 10:00-2024.10.15 21:00</t>
+          <t>2023.10.25 10:00-2024.10.20 21:00</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>996</v>
+        <v>49.9</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77530</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202310/JqP3lHJt1698030195136.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
         </is>
       </c>
     </row>
@@ -4037,38 +4037,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>上海·方块大战（豫园店）</t>
+          <t>上海·「咒术回战  × animate cafe」</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>丽水路88号2楼213 城隍庙第一购物中心</t>
+          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2023.10.25 10:00-2024.10.20 21:00</t>
+          <t>2023.12.06 00:00-2024.02.27 23:59</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>2390</v>
       </c>
       <c r="G4" t="n">
-        <v>49.9</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79057</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/ASamaqBx1701419480253.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
         </is>
       </c>
     </row>
@@ -4078,38 +4078,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·「咒术回战  × animate cafe」</t>
+          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>西藏北路198号大悦城北座8楼N809-1 animate cafe上海店</t>
+          <t>国展路1099号 上海世博展览馆</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.06 00:00-2024.02.27 23:59</t>
+          <t>2023.12.10 12:00-2024.02.16 17:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2379</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79292</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/LyD46Kty1705488020552.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
         </is>
       </c>
     </row>
@@ -4119,38 +4119,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>1739</v>
       </c>
       <c r="G6" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4160,38 +4160,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1738</v>
+        <v>980</v>
       </c>
       <c r="G7" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4201,38 +4201,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>970</v>
+        <v>1229</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4242,38 +4242,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1221</v>
+        <v>323</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4283,38 +4283,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>318</v>
+        <v>87</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4324,38 +4324,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4365,38 +4365,38 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>124</v>
+        <v>351</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4411,33 +4411,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利动漫嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>348</v>
+        <v>752</v>
       </c>
       <c r="G13" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
         </is>
       </c>
     </row>
@@ -4452,33 +4452,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>745</v>
+        <v>196</v>
       </c>
       <c r="G14" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4488,38 +4488,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4529,38 +4529,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>255</v>
       </c>
       <c r="G16" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4575,33 +4575,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第一届幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>239</v>
+        <v>1052</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
         </is>
       </c>
     </row>
@@ -4616,33 +4616,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1034</v>
+        <v>346</v>
       </c>
       <c r="G18" t="n">
-        <v>68</v>
+        <v>18.8</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4652,38 +4652,38 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>46</v>
+        <v>607</v>
       </c>
       <c r="G19" t="n">
-        <v>18.8</v>
+        <v>80</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4693,38 +4693,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>600</v>
-      </c>
-      <c r="G20" t="n">
-        <v>80</v>
+        <v>1027</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>不可售</t>
+        </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/wwR8uzxs1707103260934.jpeg</t>
         </is>
       </c>
     </row>
@@ -4734,40 +4736,38 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
+          <t>上海·SISPmini动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>剑川路1000号 龙湖上海闵行天街</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024.02.20 14:30-02.20 21:00</t>
+          <t>2024.02.24 13:00-02.25 19:00</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1017</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>不可售</t>
-        </is>
+        <v>491</v>
+      </c>
+      <c r="G21" t="n">
+        <v>48</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81740</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/wwR8uzxs1707103260934.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
         </is>
       </c>
     </row>
@@ -4782,33 +4782,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>上海·SISPmini动漫游戏嘉年华</t>
+          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>剑川路1000号 龙湖上海闵行天街</t>
+          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 14:30-02.24 16:00</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>490</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
-        <v>48</v>
+        <v>158</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79046</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/jzovdppq1706166165502.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
         </is>
       </c>
     </row>
@@ -4823,33 +4823,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>上海·SISP动漫游戏嘉年华</t>
+          <t>上海·原X铁X崩only</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>年家浜路518号 周浦万达广场</t>
+          <t>澳门路168号 月星国际家居</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2024.02.24 13:00-02.25 19:00</t>
+          <t>2024.02.24 10:30-02.24 16:30</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="G23" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80339</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202312/a8iuOufB1703832570508.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
         </is>
       </c>
     </row>
@@ -4864,33 +4864,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>上海·《哈利的魔法世界》动漫视听音乐会</t>
+          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>都市路4889号（莘庄地铁站南广场） 上海保利城市剧院</t>
+          <t>西藏南路1号 上海大世界</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2024.02.24 14:30-02.24 16:00</t>
+          <t>2024.02.24 10:00-02.25 17:00</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>15</v>
+        <v>811</v>
       </c>
       <c r="G24" t="n">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80639</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/4PieCC9N1706261750579.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
         </is>
       </c>
     </row>
@@ -4905,33 +4905,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>上海·原X铁X崩only</t>
+          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>澳门路168号 月星国际家居</t>
+          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2024.02.24 10:30-02.24 16:30</t>
+          <t>2024.02.24 11:00-02.25 16:30</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>152</v>
+        <v>2590</v>
       </c>
       <c r="G25" t="n">
-        <v>60</v>
+        <v>65.8</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81446</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/IIePRulM1706248855263.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
         </is>
       </c>
     </row>
@@ -4946,33 +4946,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>上海·原神×崩坏×星铁only旅行盛宴2.0</t>
+          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>西藏南路1号 上海大世界</t>
+          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 17:00</t>
+          <t>2024.02.24 11:30-02.25 17:30</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>808</v>
+        <v>520</v>
       </c>
       <c r="G26" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81276</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/82hU3z8m1706155835021.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
         </is>
       </c>
     </row>
@@ -4987,33 +4987,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>上海·第三届燃梦BACG PRO游戏动漫展-原X铁X崩同好交流</t>
+          <t>上海·魔都元宵节漫展-COS为王</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>盈浦街道淀山浦社区淀山湖大道851号青浦万达茂F3 万达汽车乐园(青浦万达茂店)</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2024.02.24 11:00-02.25 16:30</t>
+          <t>2024.02.24 10:00-02.25 16:00</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2588</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>65.8</v>
+        <v>49</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=77754</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202312/7eGZETK91701943985671.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
         </is>
       </c>
     </row>
@@ -5023,38 +5023,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>上海·趣元界&amp;斗罗大陆上元佳节次元派对</t>
+          <t>上海·原神X星穹铁道ONLY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>长宁路1191号长宁来福士B1 长宁来福士</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2024.02.24 11:30-02.25 17:30</t>
+          <t>2024.03.02 10:00-03.02 17:00</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>520</v>
+        <v>306</v>
       </c>
       <c r="G28" t="n">
-        <v>98</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81415</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/yis4JHfE1706169986733.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
         </is>
       </c>
     </row>
@@ -5064,38 +5064,38 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-03-02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·魔都元宵节漫展-COS为王</t>
+          <t>上海·小山百代2024上海粉丝见面会</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.02.24 10:00-02.25 16:00</t>
+          <t>2024.03.02 13:00-03.02 20:00</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>311</v>
       </c>
       <c r="G29" t="n">
-        <v>49</v>
+        <v>380</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81238</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80924</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/KxQZPADR1705913896609.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/FpA9OkKy1705467080070.jpeg</t>
         </is>
       </c>
     </row>
@@ -5105,38 +5105,38 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-03-02</t>
+          <t>2024-03-03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·原神X星穹铁道ONLY</t>
+          <t>上海·怀旧番ONLY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>逸仙路270号  上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.02 10:00-03.02 17:00</t>
+          <t>2024.03.03 10:00-03.03 17:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>306</v>
+        <v>203</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80299</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/V0xu26Cl1703753850690.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
         </is>
       </c>
     </row>
@@ -5146,38 +5146,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-03</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·怀旧番ONLY</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>逸仙路270号  上海宝丰联大酒店</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.03 10:00-03.03 17:00</t>
+          <t>2024.03.09 10:00-03.10 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80575</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/y4uWdyPT1704700763902.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
         </is>
       </c>
     </row>
@@ -5192,33 +5192,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·爱乐之城音乐会</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.03.09 10:00-03.10 17:00</t>
+          <t>2024.03.09 14:00-03.09 15:30</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>144</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81173</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81289</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/TYA5FLkE1705891815532.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/ZZXtDrwZ1705996679699.jpeg</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="G34" t="n">
         <v>73</v>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="G35" t="n">
         <v>399</v>
@@ -5351,12 +5351,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-03-16</t>
+          <t>2024-03-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
+          <t>上海·三森铃子10周年纪念2024演唱会</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5366,23 +5366,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2024.03.16 19:00-03.16 20:30</t>
+          <t>2024.03.10 18:00-03.10 19:30</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>88</v>
+        <v>569</v>
       </c>
       <c r="G36" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81433</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/L8rmm2h81706236781799.jpeg</t>
         </is>
       </c>
     </row>
@@ -5397,33 +5397,33 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·三月的幻想演唱会2024「飞越蓝色时刻」</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 19:00-03.16 20:30</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="G37" t="n">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80811</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/TO6xpSqr1705289483473.png</t>
         </is>
       </c>
     </row>
@@ -5438,33 +5438,33 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>198</v>
+        <v>54</v>
       </c>
       <c r="G38" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -5474,38 +5474,38 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>牛庄路704号 中国大戏院</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2024.03.17 15:30-03.17 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>206</v>
       </c>
       <c r="G39" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -5520,33 +5520,33 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
+          <t>上海 ·《疯狂动物城》动漫视听音乐会</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
+          <t>牛庄路704号 中国大戏院</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2024.03.17 14:00-03.17 16:00</t>
+          <t>2024.03.17 15:30-03.17 17:00</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G40" t="n">
         <v>80</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81112</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/Wg8b6SRn1705651166088.png</t>
         </is>
       </c>
     </row>
@@ -5556,38 +5556,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
+          <t>上海·遇见新海诚--帝玖「这次一定」室内乐ACG音乐会</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>南京西路1376号 上海商城剧院</t>
+          <t>延安东路523号 凯迪拉克·上海音乐厅</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2024.03.23 19:30-03.23 21:00</t>
+          <t>2024.03.17 14:00-03.17 16:00</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="G41" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81258</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/eysvN81k1705977896972.jpeg</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
+          <t>上海·《卡农Canon in D》世界经典作品视听音乐会</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5612,23 +5612,23 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2024.03.23 15:00-03.23 16:30</t>
+          <t>2024.03.23 19:30-03.23 21:00</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
         <v>50</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81358</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/Ctne29Xn1706089385959.png</t>
         </is>
       </c>
     </row>
@@ -5638,38 +5638,38 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
+          <t>上海·《四月是你的谎言》友人A经典动漫音乐会</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>宜昌路179号 万代南梦宫上海文化中心</t>
+          <t>南京西路1376号 上海商城剧院</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2024.03.29 19:00-03.29 20:30</t>
+          <t>2024.03.23 15:00-03.23 16:30</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>277</v>
+        <v>32</v>
       </c>
       <c r="G43" t="n">
-        <v>380</v>
+        <v>50</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81361</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/wL0ZWVYi1706091574963.png</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5720,38 +5720,38 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
+          <t>上海·KANAKO ITO&amp;AYANE 2024 LIVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2024.03.30 19:30-03.30 21:00</t>
+          <t>2024.03.29 19:00-03.29 20:30</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>244</v>
+        <v>282</v>
       </c>
       <c r="G45" t="n">
-        <v>680</v>
+        <v>380</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81416</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/4Y4U8tC01706172039039.jpeg</t>
         </is>
       </c>
     </row>
@@ -5766,33 +5766,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>上海·首届Redamancy动漫游戏嘉年华</t>
+          <t>上海· TRUE（唐沢美帆）上海动漫交响音乐会</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.30 19:30-03.30 21:00</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1011</v>
+        <v>248</v>
       </c>
       <c r="G46" t="n">
-        <v>60</v>
+        <v>680</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80906</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/FaJbLvS51705401178235.jpeg</t>
         </is>
       </c>
     </row>
@@ -5802,38 +5802,38 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-03-31</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
+          <t>上海·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>江宁路466号 上海艺海剧院·小剧场</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2024.03.31 10:30-03.31 12:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>1015</v>
       </c>
       <c r="G47" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
         </is>
       </c>
     </row>
@@ -5843,38 +5843,38 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-03-31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
+          <t>上海·《天空之城》宫崎骏&amp;久石让经典作品动漫视听音乐会</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>丁香路425号 上海东方艺术中心</t>
+          <t>江宁路466号 上海艺海剧院·小剧场</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2024.04.13 19:30-04.13 21:30</t>
+          <t>2024.03.31 10:30-03.31 12:00</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>191</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81660</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QKmfdsEM1706853934802.jpeg</t>
         </is>
       </c>
     </row>
@@ -5884,38 +5884,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·《四月是你的谎言》——“公生”与“薰”的钢琴小提琴唯美经典音乐集</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>丁香路425号 上海东方艺术中心</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.13 19:30-04.13 21:30</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>39</v>
+        <v>191</v>
       </c>
       <c r="G49" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78667</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/bTP7w6GD1700130122940.jpeg</t>
         </is>
       </c>
     </row>
@@ -5930,33 +5930,33 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>269</v>
+        <v>41</v>
       </c>
       <c r="G50" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -5966,36 +5966,77 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>270</v>
+      </c>
+      <c r="G51" t="n">
+        <v>79</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>33</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G52" t="n">
         <v>89</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G3" t="n">
         <v>55</v>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·奇卡波利国潮嘉年华</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -677,7 +677,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QBcbo0Do1707295657878.jpeg</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -733,33 +733,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>255</v>
+        <v>1074</v>
       </c>
       <c r="G8" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/bsBJZToU1707285951479.jpeg</t>
         </is>
       </c>
     </row>
@@ -774,33 +774,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1052</v>
+        <v>276</v>
       </c>
       <c r="G9" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G13" t="n">
         <v>80</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="G19" t="n">
         <v>65.8</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G20" t="n">
         <v>98</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
         <v>49</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>49</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25" t="n">
         <v>60</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="G28" t="n">
         <v>73</v>
@@ -1598,33 +1598,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
+          <t>上海·Look Look动漫嘉年华</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>龙吴路4800号2号门 有只怪兽片场</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.17 21:00</t>
+          <t>2024.03.16 10:00-03.17 17:30</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>40</v>
+        <v>29.9</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81804</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/WFRql6sg1707274094000.jpeg</t>
         </is>
       </c>
     </row>
@@ -1639,33 +1639,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>上海·第五人格ONLY</t>
+          <t>上海·坏孩纸物语の第33届动漫节之庄子篇</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2024.03.16 10:00-03.16 17:00</t>
+          <t>2024.03.16 10:00-03.17 21:00</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>206</v>
+        <v>54</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81138</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/jpr1lCt21705652306481.png</t>
         </is>
       </c>
     </row>
@@ -1675,38 +1675,38 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-03-30</t>
+          <t>2024-03-16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>上海·首届Redamancy动漫游戏嘉年华</t>
+          <t>上海·第五人格ONLY</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
+          <t>逸仙路301号靠纪念路路口 上海宝丰联大酒店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2024.03.30 10:00-03.31 17:00</t>
+          <t>2024.03.16 10:00-03.16 17:00</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1015</v>
+        <v>227</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81533</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/sOMO7Bjc1706604737277.png</t>
         </is>
       </c>
     </row>
@@ -1716,38 +1716,38 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-04-05</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>上海·第四届次元鹿角动漫游戏展</t>
+          <t>上海·首届Redamancy动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>顾村镇蕰川路6号 智慧湾科创园</t>
+          <t>中山北路3300号4楼L4001号 环球港上海世嘉都市乐园</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2024.04.05 10:00-04.06 17:00</t>
+          <t>2024.03.30 10:00-03.31 17:00</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>70</v>
+        <v>1022</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81772</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/XKf9RSFB1707127784856.jpeg</t>
         </is>
       </c>
     </row>
@@ -1757,38 +1757,38 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-04-05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>上海·S·CGE动漫游戏嘉年华</t>
+          <t>上海·第四届次元鹿角动漫游戏展</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>军工路1076号 纪希片场(秀场)</t>
+          <t>顾村镇蕰川路6号 智慧湾科创园</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.02 17:00</t>
+          <t>2024.04.05 10:00-04.06 17:00</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="G33" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=78228</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202311/jgqIFxhx1699344723568.jpeg</t>
         </is>
       </c>
     </row>
@@ -1803,33 +1803,33 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>上海·魔都野良神only</t>
+          <t>上海·S·CGE动漫游戏嘉年华</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>南京东路830号 第一百货</t>
+          <t>军工路1076号 纪希片场(秀场)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2024.05.01 10:00-05.01 17:00</t>
+          <t>2024.05.01 10:00-05.02 17:00</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="G34" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81204</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/nbFRULYe1705904589212.jpeg</t>
         </is>
       </c>
     </row>
@@ -1839,36 +1839,77 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>上海·魔都野良神only</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>南京东路830号 第一百货</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2024.05.01 10:00-05.01 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>270</v>
+      </c>
+      <c r="G35" t="n">
+        <v>79</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://show.bilibili.com/platform/detail.html?id=80321</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/KBlb0enU1704358750268.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>2024-05-05</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>上海·灌篮高手--青春永不散场</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>逸仙路1328弄 新业坊</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>2024.05.05 10:00-05.05 17:00</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>33</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="F36" t="n">
+        <v>34</v>
+      </c>
+      <c r="G36" t="n">
         <v>89</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>https://show.bilibili.com/platform/detail.html?id=80835</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>//i1.hdslb.com/bfs/openplatform/202401/hdaVclFC1705301931054.jpeg</t>
         </is>
@@ -2042,7 +2083,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2085,7 +2126,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2210,7 +2251,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2251,7 +2292,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
         <v>580</v>
@@ -2292,7 +2333,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="G10" t="n">
         <v>380</v>
@@ -2456,7 +2497,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="G14" t="n">
         <v>399</v>
@@ -2497,7 +2538,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G15" t="n">
         <v>380</v>
@@ -2538,7 +2579,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>80</v>
@@ -2579,7 +2620,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2663,7 +2704,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2704,7 +2745,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2788,7 +2829,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -2829,7 +2870,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
         <v>80</v>
@@ -2870,7 +2911,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -2911,7 +2952,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G25" t="n">
         <v>680</v>
@@ -2952,10 +2993,12 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2425</v>
-      </c>
-      <c r="G26" t="n">
-        <v>780</v>
+        <v>3698</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>已售罄</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3034,7 +3077,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>90</v>
@@ -3075,7 +3118,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" t="n">
         <v>80</v>
@@ -3116,7 +3159,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G30" t="n">
         <v>80</v>
@@ -3157,7 +3200,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -3239,7 +3282,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="G33" t="n">
         <v>178</v>
@@ -3280,7 +3323,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
         <v>280</v>
@@ -3321,7 +3364,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>380</v>
@@ -3462,7 +3505,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3544,7 +3587,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
         <v>49.9</v>
@@ -3585,7 +3628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2390</v>
+        <v>2401</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3626,7 +3669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3667,7 +3710,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
         <v>190</v>
@@ -3751,7 +3794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3792,7 +3835,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3833,7 +3876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -3974,7 +4017,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -4015,7 +4058,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
         <v>49.9</v>
@@ -4056,7 +4099,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2390</v>
+        <v>2401</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -4138,7 +4181,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="G6" t="n">
         <v>55</v>
@@ -4179,7 +4222,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>980</v>
+        <v>986</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -4220,7 +4263,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1229</v>
+        <v>1243</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
@@ -4261,7 +4304,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -4302,7 +4345,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -4343,7 +4386,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G11" t="n">
         <v>49</v>
@@ -4384,7 +4427,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
@@ -4411,7 +4454,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·奇卡波利动漫嘉年华</t>
+          <t>上海·奇卡波利国潮嘉年华</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4425,7 +4468,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="G13" t="n">
         <v>48.8</v>
@@ -4437,7 +4480,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/9OHovK2V1705978109130.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QBcbo0Do1707295657878.jpeg</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4509,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G14" t="n">
         <v>49</v>
@@ -4534,33 +4577,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>255</v>
+        <v>1074</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/bsBJZToU1707285951479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4575,33 +4618,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·第一届幻想物语新春动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1052</v>
+        <v>276</v>
       </c>
       <c r="G17" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/v1OFcLox1706862725129.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4673,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G18" t="n">
         <v>18.8</v>
@@ -4671,7 +4714,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -4712,7 +4755,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1027</v>
+        <v>1044</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -4755,7 +4798,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G21" t="n">
         <v>48</v>
@@ -4837,7 +4880,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -4878,7 +4921,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="G24" t="n">
         <v>65</v>
@@ -4919,7 +4962,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="G25" t="n">
         <v>65.8</v>
@@ -4960,7 +5003,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G26" t="n">
         <v>98</v>
@@ -5001,7 +5044,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
         <v>49</v>
@@ -5042,7 +5085,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G28" t="n">
         <v>60</v>
@@ -5083,7 +5126,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="G29" t="n">
         <v>380</v>
@@ -5124,7 +5167,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G30" t="n">
         <v>60</v>
@@ -5165,7 +5208,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G31" t="n">
         <v>70</v>
@@ -5247,7 +5290,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="G33" t="n">
         <v>58</v>
@@ -5288,7 +5331,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="G34" t="n">
         <v>73</v>
@@ -5329,7 +5372,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="G35" t="n">
         <v>399</v>
@@ -5370,7 +5413,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="G36" t="n">
         <v>399</v>
@@ -5411,7 +5454,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G37" t="n">
         <v>380</v>
@@ -5493,7 +5536,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="G39" t="n">
         <v>60</v>
@@ -5534,7 +5577,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
         <v>80</v>
@@ -5575,7 +5618,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G41" t="n">
         <v>80</v>
@@ -5657,7 +5700,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G43" t="n">
         <v>50</v>
@@ -5698,7 +5741,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="G44" t="n">
         <v>380</v>
@@ -5739,7 +5782,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="G45" t="n">
         <v>380</v>
@@ -5780,7 +5823,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G46" t="n">
         <v>680</v>
@@ -5821,7 +5864,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1015</v>
+        <v>1022</v>
       </c>
       <c r="G47" t="n">
         <v>60</v>
@@ -5903,7 +5946,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G49" t="n">
         <v>80</v>
@@ -5944,7 +5987,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G50" t="n">
         <v>70</v>
@@ -6026,7 +6069,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G52" t="n">
         <v>89</v>

--- a/上海-漫展信息.xlsx
+++ b/上海-漫展信息.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G4" t="n">
         <v>49</v>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="G6" t="n">
         <v>48.8</v>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G7" t="n">
         <v>49</v>
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1074</v>
+        <v>1083</v>
       </c>
       <c r="G8" t="n">
         <v>68</v>
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G9" t="n">
         <v>60</v>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G11" t="n">
         <v>18.8</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G12" t="n">
         <v>80</v>
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G14" t="n">
         <v>48</v>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G15" t="n">
         <v>48</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G17" t="n">
         <v>60</v>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="G18" t="n">
         <v>65</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="G19" t="n">
         <v>65.8</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G20" t="n">
         <v>98</v>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>49</v>
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G23" t="n">
         <v>60</v>
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G24" t="n">
         <v>60</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G26" t="n">
         <v>70</v>
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="G27" t="n">
         <v>58</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="G28" t="n">
         <v>73</v>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
         <v>29.9</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G31" t="n">
         <v>60</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="G32" t="n">
         <v>60</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G33" t="n">
         <v>60</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G35" t="n">
         <v>79</v>
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1044</v>
+        <v>1049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G8" t="n">
         <v>380</v>
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G14" t="n">
         <v>399</v>
@@ -2538,7 +2538,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G15" t="n">
         <v>380</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
         <v>80</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G22" t="n">
         <v>50</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G24" t="n">
         <v>380</v>
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3698</v>
+        <v>3759</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G31" t="n">
         <v>280</v>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="G33" t="n">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G34" t="n">
         <v>280</v>
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2401</v>
+        <v>2406</v>
       </c>
       <c r="G5" t="n">
         <v>30</v>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="G6" t="n">
         <v>10</v>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="G10" t="n">
         <v>30</v>
@@ -3876,7 +3876,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" t="n">
         <v>30</v>
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2401</v>
+        <v>2406</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -4121,38 +4121,38 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>上海·多维跃迁-2023 红点设计概念大奖获奖作品展</t>
+          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>国展路1099号 上海世博展览馆</t>
+          <t>湖滨路168号 上海无限极荟购物中心</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2023.12.10 12:00-2024.02.16 17:00</t>
+          <t>2023.12.22 10:00-2024.02.16 22:00</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>37</v>
+        <v>1740</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=78809</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/YsBoZAOW1700551290654.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
         </is>
       </c>
     </row>
@@ -4162,38 +4162,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-12-22</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>上海·新海诚导演作品《铃芽之旅》展 丨 购票抽新海诚见面会门票丨 超限定复刻原画发售</t>
+          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>湖滨路168号 上海无限极荟购物中心</t>
+          <t>南京东路340号 百联zx创趣场</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2023.12.22 10:00-2024.02.16 22:00</t>
+          <t>2024.01.06 00:00-02.29 23:59</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1740</v>
+        <v>989</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=79166</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202311/MjTiIYlk1701242361853.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
         </is>
       </c>
     </row>
@@ -4203,38 +4203,38 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-01-06</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>上海·罗小黑 x HAPPY ZOO主题Cafe</t>
+          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南京东路340号 百联zx创趣场</t>
+          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2024.01.06 00:00-02.29 23:59</t>
+          <t>2024.01.27 00:00-03.31 23:59</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>986</v>
+        <v>1248</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80171</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202312/chPePM8d1703485388734.png</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
         </is>
       </c>
     </row>
@@ -4244,38 +4244,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>上海・明日方舟主题店·[SWEET ZONE甜蜜区域]</t>
+          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>南京东路830号第一百货商业中心B馆5楼(海底捞旁边) 第一百货商业中心</t>
+          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2024.01.27 00:00-03.31 23:59</t>
+          <t>2024.02.01 00:00-03.01 23:59</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1243</v>
+        <v>332</v>
       </c>
       <c r="G8" t="n">
         <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81277</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/hp6D0Drt1705991831205.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
         </is>
       </c>
     </row>
@@ -4285,38 +4285,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>上海·次元波板糖×线条小狗MALTESE 主题快闪店</t>
+          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>西藏北路166静安大悦城北座6楼611号 次元波板糖</t>
+          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2024.02.01 00:00-03.01 23:59</t>
+          <t>2024.02.02 00:00-03.10 23:59</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>327</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
         <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81345</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/Qbpful951706080847394.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
         </is>
       </c>
     </row>
@@ -4326,38 +4326,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-02-10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>上海·2024《永远的7日之都》x  萌果酱谷子咖啡</t>
+          <t>上海·寒假CF漫展-春节档-神龙在世</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>南京东路340号百联ZX 萌果酱谷子咖啡（百联）</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2024.02.02 00:00-03.10 23:59</t>
+          <t>2024.02.10 10:00-02.17 16:00</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81357</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/5OYoWSGL1706087914805.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
         </is>
       </c>
     </row>
@@ -4367,38 +4367,38 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-02-10</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上海·寒假CF漫展-春节档-神龙在世</t>
+          <t>上海·Coser新春拜年盛典</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2024.02.10 10:00-02.17 16:00</t>
+          <t>2024.02.14 10:00-02.15 17:00</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>132</v>
+        <v>374</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81192</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/S8XxkA631705896741998.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
         </is>
       </c>
     </row>
@@ -4413,33 +4413,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上海·Coser新春拜年盛典</t>
+          <t>上海·奇卡波利国潮嘉年华</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>申滨路36号 虹桥丽宝广场</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.15 17:00</t>
+          <t>2024.02.14 10:00-02.14 17:00</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>364</v>
+        <v>769</v>
       </c>
       <c r="G12" t="n">
-        <v>60</v>
+        <v>48.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81588</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>//i1.hdslb.com/bfs/openplatform/202402/FZxjoQH41706757037933.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/QBcbo0Do1707295657878.jpeg</t>
         </is>
       </c>
     </row>
@@ -4454,33 +4454,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上海·奇卡波利国潮嘉年华</t>
+          <t>上海·魔都COS漫展-情人节专场AM01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>申滨路36号 虹桥丽宝广场</t>
+          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 17:00</t>
+          <t>2024.02.14 10:00-02.14 16:00</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>760</v>
+        <v>210</v>
       </c>
       <c r="G13" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81260</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/QBcbo0Do1707295657878.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
         </is>
       </c>
     </row>
@@ -4490,38 +4490,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-02-14</t>
+          <t>2024-02-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>上海·魔都COS漫展-情人节专场AM01</t>
+          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>澳门路168号月星家居(江宁路地铁站1号口步行420米) 月星广场</t>
+          <t>曹杨路1888号 上海露边社·演艺空间</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2024.02.14 10:00-02.14 16:00</t>
+          <t>2024.02.15 19:00-03.03 20:10</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>204</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=80691</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/aSdjV6Kw1704868345679.jpeg</t>
+          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
         </is>
       </c>
     </row>
@@ -4531,38 +4531,38 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-02-15</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上海·飘起来吧魔法泡泡-魔术表演</t>
+          <t>上海·幻想物语新春动漫嘉年华</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>曹杨路1888号 上海露边社·演艺空间</t>
+          <t>长寿路309号 旭辉企业大厦</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2024.02.15 19:00-03.03 20:10</t>
+          <t>2024.02.16 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>1083</v>
       </c>
       <c r="G15" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81524</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>//i0.hdslb.com/bfs/openplatform/202401/tls18D0J1706599640356.png</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/bsBJZToU1707285951479.jpeg</t>
         </is>
       </c>
     </row>
@@ -4577,33 +4577,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海·幻想物语新春动漫嘉年华</t>
+          <t>上海·次元裂缝-X 新年anikura派对</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>长寿路309号 旭辉企业大厦</t>
+          <t>海潮路133号B1 JUMP工坊</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2024.02.16 10:00-02.17 17:00</t>
+          <t>2024.02.16 14:00-02.16 19:00</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1074</v>
+        <v>279</v>
       </c>
       <c r="G16" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81682</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/bsBJZToU1707285951479.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
         </is>
       </c>
     </row>
@@ -4618,33 +4618,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海·次元裂缝-X 新年anikura派对</t>
+          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>海潮路133号B1 JUMP工坊</t>
+          <t>云台路 800号 最家空间·亿丰时代广场</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2024.02.16 14:00-02.16 19:00</t>
+          <t>2024.02.16 11:00-02.17 16:30</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>276</v>
+        <v>352</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>18.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81314</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202401/OrhHWKdR1706062360956.jpeg</t>
+          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
         </is>
       </c>
     </row>
@@ -4654,38 +4654,38 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-02-17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海·第五十四届燃梦星辰动漫展-枫丹启动&amp;梦回匹诺康尼</t>
+          <t>上海·少女番only2.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>云台路 800号 最家空间·亿丰时代广场</t>
+          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2024.02.16 11:00-02.17 16:30</t>
+          <t>2024.02.17 10:00-02.17 17:00</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>350</v>
+        <v>628</v>
       </c>
       <c r="G18" t="n">
-        <v>18.8</v>
+        <v>80</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://show.bilibili.com/platform/detail.html?id=81576</t>
+          <t>https://show.bilibili.com/platform/detail.html?id=81148</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>//i2.hdslb.com/bfs/openplatform/202402/KEby3fBG1706772461373.jpeg</t>
+          <t>//i1.hdslb.com/bfs/openplatform/202401/j6eEZ18S1705657346664.jpeg</t>
         </is>
       </c>
     </row>
@@ -4695,38 +4695,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-02-17</t>
+          <t>2024-02-20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>上海·少女番only2.0</t>
+          <t>上海·Liyuu 「鲤好！」粉丝见面会</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>营口路699号(黄兴公园地铁站2号口旁) 花嫁丽舍</t>
+          <t>宜昌路179号 万代南梦宫上海文化中心</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024.02.17 10:00-02.17 17:00</t>
+          <t>2024.02.20 14:30-02.20 21:00</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>625</v>
-      </c>
-      <c r="G19" t="n">
-        <v>80</v>
+        <v>1049</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+        